--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 лгрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\25,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60331175-1B90-4B62-8BCD-A29AA8C49D96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623D58EA-84D8-404A-85E8-FC8EC53B3B11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$134</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2347,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK500"/>
+  <dimension ref="A1:AL500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -2369,7 +2369,7 @@
     <col min="37" max="37" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2410,7 +2410,7 @@
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -2451,7 +2451,7 @@
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -2639,7 +2639,7 @@
       <c r="AJ4" s="11"/>
       <c r="AK4" s="11"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -2755,8 +2755,12 @@
         <f>SUM(AK6:AK500)</f>
         <v>10348</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL5" s="3">
+        <f>SUM(AL6:AL500)</f>
+        <v>7593.1963999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>38</v>
       </c>
@@ -2856,8 +2860,12 @@
         <f>ROUND(G6*W6,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL6">
+        <f>U6*G6</f>
+        <v>483.68119999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>41</v>
       </c>
@@ -2960,8 +2968,12 @@
         <f t="shared" ref="AK7:AK70" si="6">ROUND(G7*W7,0)</f>
         <v>542</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL7">
+        <f t="shared" ref="AL7:AL70" si="7">U7*G7</f>
+        <v>307.12900000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>42</v>
       </c>
@@ -3064,8 +3076,12 @@
         <f t="shared" si="6"/>
         <v>460</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL8">
+        <f t="shared" si="7"/>
+        <v>254.85239999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>43</v>
       </c>
@@ -3105,7 +3121,7 @@
       </c>
       <c r="V9" s="10"/>
       <c r="W9" s="4">
-        <f t="shared" ref="W9:W70" si="7">V9</f>
+        <f t="shared" ref="W9:W70" si="8">V9</f>
         <v>0</v>
       </c>
       <c r="X9" s="11" t="e">
@@ -3153,8 +3169,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>46</v>
       </c>
@@ -3213,7 +3233,7 @@
         <v>131.28799999999978</v>
       </c>
       <c r="W10" s="4">
-        <f t="shared" ref="W10:W11" si="8">V10+$W$1*U10</f>
+        <f t="shared" ref="W10:W11" si="9">V10+$W$1*U10</f>
         <v>253.88799999999978</v>
       </c>
       <c r="X10" s="11">
@@ -3259,8 +3279,12 @@
         <f t="shared" si="6"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL10">
+        <f t="shared" si="7"/>
+        <v>55.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>47</v>
       </c>
@@ -3317,7 +3341,7 @@
         <v>180.06740000000104</v>
       </c>
       <c r="W11" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>428.26740000000103</v>
       </c>
       <c r="X11" s="11">
@@ -3363,8 +3387,12 @@
         <f t="shared" si="6"/>
         <v>193</v>
       </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL11">
+        <f t="shared" si="7"/>
+        <v>111.69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>48</v>
       </c>
@@ -3416,7 +3444,7 @@
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X12" s="11">
@@ -3462,8 +3490,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL12">
+        <f t="shared" si="7"/>
+        <v>2.1760000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>49</v>
       </c>
@@ -3515,7 +3547,7 @@
         <v>50</v>
       </c>
       <c r="W13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="X13" s="11">
@@ -3561,8 +3593,12 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL13">
+        <f t="shared" si="7"/>
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>51</v>
       </c>
@@ -3614,7 +3650,7 @@
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X14" s="11">
@@ -3660,8 +3696,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL14">
+        <f t="shared" si="7"/>
+        <v>8.0920000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>52</v>
       </c>
@@ -3705,7 +3745,7 @@
       </c>
       <c r="V15" s="10"/>
       <c r="W15" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X15" s="11" t="e">
@@ -3751,8 +3791,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>54</v>
       </c>
@@ -3806,7 +3850,7 @@
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X16" s="11">
@@ -3852,8 +3896,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL16">
+        <f t="shared" si="7"/>
+        <v>217.41739999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>55</v>
       </c>
@@ -3909,7 +3957,7 @@
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X17" s="11">
@@ -3955,8 +4003,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL17">
+        <f t="shared" si="7"/>
+        <v>674.39080000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>56</v>
       </c>
@@ -4008,7 +4060,7 @@
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X18" s="11">
@@ -4054,8 +4106,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL18">
+        <f t="shared" si="7"/>
+        <v>19.870200000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>57</v>
       </c>
@@ -4107,7 +4163,7 @@
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X19" s="11">
@@ -4153,8 +4209,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL19">
+        <f t="shared" si="7"/>
+        <v>16.345400000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>58</v>
       </c>
@@ -4204,7 +4264,7 @@
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X20" s="11">
@@ -4250,8 +4310,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL20">
+        <f t="shared" si="7"/>
+        <v>1.3657999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>59</v>
       </c>
@@ -4305,7 +4369,7 @@
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X21" s="11">
@@ -4351,8 +4415,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL21">
+        <f t="shared" si="7"/>
+        <v>253.47559999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>60</v>
       </c>
@@ -4404,7 +4472,7 @@
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X22" s="11">
@@ -4450,8 +4518,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL22">
+        <f t="shared" si="7"/>
+        <v>36.369999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>61</v>
       </c>
@@ -4510,7 +4582,7 @@
         <v>24.148495399999774</v>
       </c>
       <c r="W23" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.148495399999774</v>
       </c>
       <c r="X23" s="11">
@@ -4556,8 +4628,12 @@
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL23">
+        <f t="shared" si="7"/>
+        <v>76.412599999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>62</v>
       </c>
@@ -4597,7 +4673,7 @@
       </c>
       <c r="V24" s="10"/>
       <c r="W24" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X24" s="11" t="e">
@@ -4645,8 +4721,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>63</v>
       </c>
@@ -4705,7 +4785,7 @@
         <v>14.170343199999706</v>
       </c>
       <c r="W25" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14.170343199999706</v>
       </c>
       <c r="X25" s="11">
@@ -4751,8 +4831,12 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL25">
+        <f t="shared" si="7"/>
+        <v>117.58959999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>64</v>
       </c>
@@ -4810,7 +4894,7 @@
         <v>80</v>
       </c>
       <c r="W26" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="X26" s="11">
@@ -4856,8 +4940,12 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL26">
+        <f t="shared" si="7"/>
+        <v>18.895199999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>65</v>
       </c>
@@ -4912,7 +5000,7 @@
         <v>251.35111400000005</v>
       </c>
       <c r="W27" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>251.35111400000005</v>
       </c>
       <c r="X27" s="11">
@@ -4958,8 +5046,12 @@
         <f t="shared" si="6"/>
         <v>251</v>
       </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL27">
+        <f t="shared" si="7"/>
+        <v>63.1462</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>66</v>
       </c>
@@ -5017,7 +5109,7 @@
         <v>100</v>
       </c>
       <c r="W28" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="X28" s="11">
@@ -5063,8 +5155,12 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL28">
+        <f t="shared" si="7"/>
+        <v>-1.6392</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>67</v>
       </c>
@@ -5123,7 +5219,7 @@
         <v>1060.5351000000001</v>
       </c>
       <c r="W29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1060.5351000000001</v>
       </c>
       <c r="X29" s="11">
@@ -5169,8 +5265,12 @@
         <f t="shared" si="6"/>
         <v>1061</v>
       </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL29">
+        <f t="shared" si="7"/>
+        <v>403.56360000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>68</v>
       </c>
@@ -5218,7 +5318,7 @@
       </c>
       <c r="V30" s="10"/>
       <c r="W30" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X30" s="11" t="e">
@@ -5264,8 +5364,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>69</v>
       </c>
@@ -5313,7 +5417,7 @@
       </c>
       <c r="V31" s="10"/>
       <c r="W31" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X31" s="11" t="e">
@@ -5359,8 +5463,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>70</v>
       </c>
@@ -5461,8 +5569,12 @@
         <f t="shared" si="6"/>
         <v>1400</v>
       </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL32">
+        <f t="shared" si="7"/>
+        <v>116.49420000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>71</v>
       </c>
@@ -5502,7 +5614,7 @@
       </c>
       <c r="V33" s="10"/>
       <c r="W33" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X33" s="11" t="e">
@@ -5550,8 +5662,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL33">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>72</v>
       </c>
@@ -5605,7 +5721,7 @@
       </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X34" s="11">
@@ -5651,8 +5767,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL34">
+        <f t="shared" si="7"/>
+        <v>31.436399999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>73</v>
       </c>
@@ -5692,7 +5812,7 @@
       </c>
       <c r="V35" s="10"/>
       <c r="W35" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X35" s="11" t="e">
@@ -5740,8 +5860,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>74</v>
       </c>
@@ -5781,7 +5905,7 @@
       </c>
       <c r="V36" s="10"/>
       <c r="W36" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X36" s="11" t="e">
@@ -5829,8 +5953,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>75</v>
       </c>
@@ -5931,8 +6059,12 @@
         <f t="shared" si="6"/>
         <v>1480</v>
       </c>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL37">
+        <f t="shared" si="7"/>
+        <v>304.56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>76</v>
       </c>
@@ -5965,7 +6097,7 @@
         <v>437</v>
       </c>
       <c r="L38" s="11">
-        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="10">E38-K38</f>
         <v>-11</v>
       </c>
       <c r="M38" s="11"/>
@@ -5981,12 +6113,12 @@
       <c r="S38" s="11"/>
       <c r="T38" s="11"/>
       <c r="U38" s="11">
-        <f t="shared" ref="U38:U69" si="10">E38/5</f>
+        <f t="shared" ref="U38:U69" si="11">E38/5</f>
         <v>85.2</v>
       </c>
       <c r="V38" s="4"/>
       <c r="W38" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X38" s="11">
@@ -5994,7 +6126,7 @@
         <v>12.391579812206572</v>
       </c>
       <c r="Y38" s="11">
-        <f t="shared" ref="Y38:Y69" si="11">(F38+O38+P38+Q38+R38+S38+T38)/U38</f>
+        <f t="shared" ref="Y38:Y69" si="12">(F38+O38+P38+Q38+R38+S38+T38)/U38</f>
         <v>12.391579812206572</v>
       </c>
       <c r="Z38" s="11">
@@ -6032,8 +6164,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL38">
+        <f t="shared" si="7"/>
+        <v>38.340000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>77</v>
       </c>
@@ -6064,7 +6200,7 @@
         <v>646</v>
       </c>
       <c r="L39" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-652</v>
       </c>
       <c r="M39" s="11"/>
@@ -6082,14 +6218,14 @@
       <c r="S39" s="11"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.2</v>
       </c>
       <c r="V39" s="4">
         <v>300</v>
       </c>
       <c r="W39" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="X39" s="11">
@@ -6097,7 +6233,7 @@
         <v>-390</v>
       </c>
       <c r="Y39" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-140</v>
       </c>
       <c r="Z39" s="11">
@@ -6135,8 +6271,12 @@
         <f t="shared" si="6"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL39">
+        <f t="shared" si="7"/>
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>78</v>
       </c>
@@ -6163,7 +6303,7 @@
         <v>2</v>
       </c>
       <c r="L40" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3</v>
       </c>
       <c r="M40" s="11"/>
@@ -6183,14 +6323,14 @@
       </c>
       <c r="T40" s="11"/>
       <c r="U40" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.2</v>
       </c>
       <c r="V40" s="4">
         <v>10</v>
       </c>
       <c r="W40" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="X40" s="11">
@@ -6198,7 +6338,7 @@
         <v>-17.5</v>
       </c>
       <c r="Y40" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>32.5</v>
       </c>
       <c r="Z40" s="11">
@@ -6236,8 +6376,12 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL40">
+        <f t="shared" si="7"/>
+        <v>-8.0000000000000016E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>79</v>
       </c>
@@ -6270,7 +6414,7 @@
         <v>282.8</v>
       </c>
       <c r="L41" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.56900000000001683</v>
       </c>
       <c r="M41" s="11"/>
@@ -6286,7 +6430,7 @@
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
       <c r="U41" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>56.673800000000007</v>
       </c>
       <c r="V41" s="4">
@@ -6294,7 +6438,7 @@
         <v>213.84406680000009</v>
       </c>
       <c r="W41" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>213.84406680000009</v>
       </c>
       <c r="X41" s="11">
@@ -6302,7 +6446,7 @@
         <v>11</v>
       </c>
       <c r="Y41" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.2267561589305815</v>
       </c>
       <c r="Z41" s="11">
@@ -6340,8 +6484,12 @@
         <f t="shared" si="6"/>
         <v>214</v>
       </c>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL41">
+        <f t="shared" si="7"/>
+        <v>56.673800000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>80</v>
       </c>
@@ -6374,7 +6522,7 @@
         <v>399</v>
       </c>
       <c r="L42" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M42" s="11"/>
@@ -6388,7 +6536,7 @@
       <c r="S42" s="11"/>
       <c r="T42" s="11"/>
       <c r="U42" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>79.8</v>
       </c>
       <c r="V42" s="4">
@@ -6396,7 +6544,7 @@
         <v>366.59999999999991</v>
       </c>
       <c r="W42" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>366.59999999999991</v>
       </c>
       <c r="X42" s="11">
@@ -6404,7 +6552,7 @@
         <v>11</v>
       </c>
       <c r="Y42" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.4060150375939848</v>
       </c>
       <c r="Z42" s="11">
@@ -6442,8 +6590,12 @@
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL42">
+        <f t="shared" si="7"/>
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>81</v>
       </c>
@@ -6474,7 +6626,7 @@
         <v>64</v>
       </c>
       <c r="L43" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-73</v>
       </c>
       <c r="M43" s="11"/>
@@ -6494,14 +6646,14 @@
       </c>
       <c r="T43" s="11"/>
       <c r="U43" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.8</v>
       </c>
       <c r="V43" s="4">
         <v>100</v>
       </c>
       <c r="W43" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="X43" s="11">
@@ -6509,7 +6661,7 @@
         <v>-51.507936507936506</v>
       </c>
       <c r="Y43" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.047619047619051</v>
       </c>
       <c r="Z43" s="11">
@@ -6547,8 +6699,12 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL43">
+        <f t="shared" si="7"/>
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>82</v>
       </c>
@@ -6581,7 +6737,7 @@
         <v>47.25</v>
       </c>
       <c r="L44" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-41.436</v>
       </c>
       <c r="M44" s="11"/>
@@ -6601,14 +6757,14 @@
       </c>
       <c r="T44" s="11"/>
       <c r="U44" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1628000000000001</v>
       </c>
       <c r="V44" s="4">
         <v>20</v>
       </c>
       <c r="W44" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="X44" s="11">
@@ -6616,7 +6772,7 @@
         <v>42.131062951496396</v>
       </c>
       <c r="Y44" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24.931200550395598</v>
       </c>
       <c r="Z44" s="11">
@@ -6654,8 +6810,12 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL44">
+        <f t="shared" si="7"/>
+        <v>1.1628000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>83</v>
       </c>
@@ -6688,7 +6848,7 @@
         <v>264</v>
       </c>
       <c r="L45" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-82</v>
       </c>
       <c r="M45" s="11"/>
@@ -6704,7 +6864,7 @@
       <c r="S45" s="11"/>
       <c r="T45" s="11"/>
       <c r="U45" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
       <c r="V45" s="4">
@@ -6712,7 +6872,7 @@
         <v>218.39999999999998</v>
       </c>
       <c r="W45" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>218.39999999999998</v>
       </c>
       <c r="X45" s="11">
@@ -6720,7 +6880,7 @@
         <v>11</v>
       </c>
       <c r="Y45" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Z45" s="11">
@@ -6758,8 +6918,12 @@
         <f t="shared" si="6"/>
         <v>87</v>
       </c>
-    </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL45">
+        <f t="shared" si="7"/>
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>84</v>
       </c>
@@ -6792,7 +6956,7 @@
         <v>284</v>
       </c>
       <c r="L46" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-133</v>
       </c>
       <c r="M46" s="11"/>
@@ -6808,7 +6972,7 @@
       <c r="S46" s="11"/>
       <c r="T46" s="11"/>
       <c r="U46" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>30.2</v>
       </c>
       <c r="V46" s="4">
@@ -6816,7 +6980,7 @@
         <v>173.2</v>
       </c>
       <c r="W46" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>173.2</v>
       </c>
       <c r="X46" s="11">
@@ -6824,7 +6988,7 @@
         <v>11</v>
       </c>
       <c r="Y46" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.2649006622516561</v>
       </c>
       <c r="Z46" s="11">
@@ -6862,8 +7026,12 @@
         <f t="shared" si="6"/>
         <v>69</v>
       </c>
-    </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL46">
+        <f t="shared" si="7"/>
+        <v>12.08</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>85</v>
       </c>
@@ -6896,7 +7064,7 @@
         <v>135.65</v>
       </c>
       <c r="L47" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-13.309000000000012</v>
       </c>
       <c r="M47" s="11"/>
@@ -6912,14 +7080,14 @@
       <c r="S47" s="11"/>
       <c r="T47" s="11"/>
       <c r="U47" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24.4682</v>
       </c>
       <c r="V47" s="4">
         <v>80</v>
       </c>
       <c r="W47" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="X47" s="11">
@@ -6927,7 +7095,7 @@
         <v>6.312969486925887</v>
       </c>
       <c r="Y47" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.0434196222035124</v>
       </c>
       <c r="Z47" s="11">
@@ -6965,8 +7133,12 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL47">
+        <f t="shared" si="7"/>
+        <v>24.4682</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>86</v>
       </c>
@@ -6999,7 +7171,7 @@
         <v>1531</v>
       </c>
       <c r="L48" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-341</v>
       </c>
       <c r="M48" s="11"/>
@@ -7019,14 +7191,14 @@
       </c>
       <c r="T48" s="11"/>
       <c r="U48" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>238</v>
       </c>
       <c r="V48" s="4">
         <v>800</v>
       </c>
       <c r="W48" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>800</v>
       </c>
       <c r="X48" s="11">
@@ -7034,7 +7206,7 @@
         <v>3.3145258103241293</v>
       </c>
       <c r="Y48" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.6818727490996741E-2</v>
       </c>
       <c r="Z48" s="11">
@@ -7072,8 +7244,12 @@
         <f t="shared" si="6"/>
         <v>280</v>
       </c>
-    </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL48">
+        <f t="shared" si="7"/>
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>87</v>
       </c>
@@ -7106,7 +7282,7 @@
         <v>721</v>
       </c>
       <c r="L49" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-7</v>
       </c>
       <c r="M49" s="11"/>
@@ -7122,7 +7298,7 @@
       <c r="S49" s="11"/>
       <c r="T49" s="11"/>
       <c r="U49" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>142.80000000000001</v>
       </c>
       <c r="V49" s="4">
@@ -7130,7 +7306,7 @@
         <v>136.80000000000018</v>
       </c>
       <c r="W49" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>136.80000000000018</v>
       </c>
       <c r="X49" s="11">
@@ -7138,7 +7314,7 @@
         <v>11</v>
       </c>
       <c r="Y49" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.042016806722689</v>
       </c>
       <c r="Z49" s="11">
@@ -7176,8 +7352,12 @@
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL49">
+        <f t="shared" si="7"/>
+        <v>57.120000000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>88</v>
       </c>
@@ -7210,7 +7390,7 @@
         <v>440.75</v>
       </c>
       <c r="L50" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0670000000000073</v>
       </c>
       <c r="M50" s="11"/>
@@ -7226,7 +7406,7 @@
       <c r="S50" s="11"/>
       <c r="T50" s="11"/>
       <c r="U50" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>89.163399999999996</v>
       </c>
       <c r="V50" s="4">
@@ -7242,7 +7422,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="Y50" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.387109253348347</v>
       </c>
       <c r="Z50" s="11">
@@ -7280,8 +7460,12 @@
         <f t="shared" si="6"/>
         <v>144</v>
       </c>
-    </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL50">
+        <f t="shared" si="7"/>
+        <v>89.163399999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>89</v>
       </c>
@@ -7314,7 +7498,7 @@
         <v>532.45000000000005</v>
       </c>
       <c r="L51" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.8919999999999391</v>
       </c>
       <c r="M51" s="11"/>
@@ -7330,12 +7514,12 @@
       <c r="S51" s="11"/>
       <c r="T51" s="11"/>
       <c r="U51" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107.86839999999999</v>
       </c>
       <c r="V51" s="4"/>
       <c r="W51" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X51" s="11">
@@ -7343,7 +7527,7 @@
         <v>11.545798869733867</v>
       </c>
       <c r="Y51" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11.545798869733867</v>
       </c>
       <c r="Z51" s="11">
@@ -7381,8 +7565,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL51">
+        <f t="shared" si="7"/>
+        <v>107.86839999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>90</v>
       </c>
@@ -7411,7 +7599,7 @@
         <v>98.7</v>
       </c>
       <c r="L52" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-98.7</v>
       </c>
       <c r="M52" s="11"/>
@@ -7431,14 +7619,14 @@
       </c>
       <c r="T52" s="11"/>
       <c r="U52" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V52" s="4">
         <v>20</v>
       </c>
       <c r="W52" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="X52" s="11" t="e">
@@ -7446,7 +7634,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y52" s="11" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z52" s="11">
@@ -7486,8 +7674,12 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL52">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>92</v>
       </c>
@@ -7520,7 +7712,7 @@
         <v>186</v>
       </c>
       <c r="L53" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-4</v>
       </c>
       <c r="M53" s="11"/>
@@ -7534,7 +7726,7 @@
       <c r="S53" s="11"/>
       <c r="T53" s="11"/>
       <c r="U53" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
       <c r="V53" s="4">
@@ -7542,7 +7734,7 @@
         <v>159.39999999999998</v>
       </c>
       <c r="W53" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>159.39999999999998</v>
       </c>
       <c r="X53" s="11">
@@ -7550,7 +7742,7 @@
         <v>11</v>
       </c>
       <c r="Y53" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.6208791208791213</v>
       </c>
       <c r="Z53" s="11">
@@ -7588,8 +7780,12 @@
         <f t="shared" si="6"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL53">
+        <f t="shared" si="7"/>
+        <v>16.38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>93</v>
       </c>
@@ -7622,7 +7818,7 @@
         <v>484</v>
       </c>
       <c r="L54" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-20</v>
       </c>
       <c r="M54" s="11"/>
@@ -7638,7 +7834,7 @@
       <c r="S54" s="11"/>
       <c r="T54" s="11"/>
       <c r="U54" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>92.8</v>
       </c>
       <c r="V54" s="4">
@@ -7654,7 +7850,7 @@
         <v>12</v>
       </c>
       <c r="Y54" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.787234913793105</v>
       </c>
       <c r="Z54" s="11">
@@ -7692,8 +7888,12 @@
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-    </row>
-    <row r="55" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL54">
+        <f t="shared" si="7"/>
+        <v>41.76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>94</v>
       </c>
@@ -7722,7 +7922,7 @@
         <v>125</v>
       </c>
       <c r="L55" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-38</v>
       </c>
       <c r="M55" s="11"/>
@@ -7742,14 +7942,14 @@
       </c>
       <c r="T55" s="11"/>
       <c r="U55" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>17.399999999999999</v>
       </c>
       <c r="V55" s="4">
         <v>80</v>
       </c>
       <c r="W55" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="X55" s="11">
@@ -7757,7 +7957,7 @@
         <v>4.2241379310344831</v>
       </c>
       <c r="Y55" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.37356321839080464</v>
       </c>
       <c r="Z55" s="11">
@@ -7795,8 +7995,12 @@
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL55">
+        <f t="shared" si="7"/>
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>95</v>
       </c>
@@ -7829,7 +8033,7 @@
         <v>82</v>
       </c>
       <c r="L56" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-23</v>
       </c>
       <c r="M56" s="11"/>
@@ -7845,12 +8049,12 @@
       <c r="S56" s="11"/>
       <c r="T56" s="11"/>
       <c r="U56" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11.8</v>
       </c>
       <c r="V56" s="4"/>
       <c r="W56" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X56" s="11">
@@ -7858,7 +8062,7 @@
         <v>14.355932203389832</v>
       </c>
       <c r="Y56" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.355932203389832</v>
       </c>
       <c r="Z56" s="11">
@@ -7896,8 +8100,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL56">
+        <f t="shared" si="7"/>
+        <v>4.7200000000000006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>96</v>
       </c>
@@ -7930,7 +8138,7 @@
         <v>655.15</v>
       </c>
       <c r="L57" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.461000000000013</v>
       </c>
       <c r="M57" s="11"/>
@@ -7948,12 +8156,12 @@
       <c r="S57" s="11"/>
       <c r="T57" s="11"/>
       <c r="U57" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>135.32220000000001</v>
       </c>
       <c r="V57" s="4"/>
       <c r="W57" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X57" s="11">
@@ -7961,7 +8169,7 @@
         <v>11.627693739829827</v>
       </c>
       <c r="Y57" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11.627693739829827</v>
       </c>
       <c r="Z57" s="11">
@@ -7999,8 +8207,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL57">
+        <f t="shared" si="7"/>
+        <v>135.32220000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>97</v>
       </c>
@@ -8027,7 +8239,7 @@
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M58" s="8"/>
@@ -8041,12 +8253,12 @@
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
       <c r="U58" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V58" s="10"/>
       <c r="W58" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X58" s="11" t="e">
@@ -8054,7 +8266,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y58" s="11" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z58" s="8">
@@ -8092,8 +8304,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>100</v>
       </c>
@@ -8126,7 +8342,7 @@
         <v>242</v>
       </c>
       <c r="L59" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-5</v>
       </c>
       <c r="M59" s="11"/>
@@ -8140,7 +8356,7 @@
       <c r="S59" s="11"/>
       <c r="T59" s="11"/>
       <c r="U59" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>47.4</v>
       </c>
       <c r="V59" s="4">
@@ -8148,7 +8364,7 @@
         <v>245.99999999999994</v>
       </c>
       <c r="W59" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>245.99999999999994</v>
       </c>
       <c r="X59" s="11">
@@ -8156,7 +8372,7 @@
         <v>11</v>
       </c>
       <c r="Y59" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.8101265822784818</v>
       </c>
       <c r="Z59" s="11">
@@ -8194,8 +8410,12 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL59">
+        <f t="shared" si="7"/>
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>101</v>
       </c>
@@ -8228,7 +8448,7 @@
         <v>745.1</v>
       </c>
       <c r="L60" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23.496999999999957</v>
       </c>
       <c r="M60" s="11"/>
@@ -8244,7 +8464,7 @@
       <c r="S60" s="11"/>
       <c r="T60" s="11"/>
       <c r="U60" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>153.71940000000001</v>
       </c>
       <c r="V60" s="4"/>
@@ -8256,7 +8476,7 @@
         <v>13.391745468691651</v>
       </c>
       <c r="Y60" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12.415941503804982</v>
       </c>
       <c r="Z60" s="11">
@@ -8294,8 +8514,12 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="61" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL60">
+        <f t="shared" si="7"/>
+        <v>153.71940000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>102</v>
       </c>
@@ -8328,7 +8552,7 @@
         <v>104.45</v>
       </c>
       <c r="L61" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.8840000000000003</v>
       </c>
       <c r="M61" s="11"/>
@@ -8342,7 +8566,7 @@
       <c r="S61" s="11"/>
       <c r="T61" s="11"/>
       <c r="U61" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21.666800000000002</v>
       </c>
       <c r="V61" s="4">
@@ -8350,7 +8574,7 @@
         <v>123.35580000000003</v>
       </c>
       <c r="W61" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>123.35580000000003</v>
       </c>
       <c r="X61" s="11">
@@ -8358,7 +8582,7 @@
         <v>11</v>
       </c>
       <c r="Y61" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.3066904203666434</v>
       </c>
       <c r="Z61" s="11">
@@ -8396,8 +8620,12 @@
         <f t="shared" si="6"/>
         <v>123</v>
       </c>
-    </row>
-    <row r="62" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL61">
+        <f t="shared" si="7"/>
+        <v>21.666800000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>103</v>
       </c>
@@ -8430,7 +8658,7 @@
         <v>190</v>
       </c>
       <c r="L62" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M62" s="11"/>
@@ -8444,7 +8672,7 @@
       <c r="S62" s="11"/>
       <c r="T62" s="11"/>
       <c r="U62" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
       <c r="V62" s="4">
@@ -8452,7 +8680,7 @@
         <v>152</v>
       </c>
       <c r="W62" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>152</v>
       </c>
       <c r="X62" s="11">
@@ -8460,7 +8688,7 @@
         <v>11</v>
       </c>
       <c r="Y62" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Z62" s="11">
@@ -8498,8 +8726,12 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL62">
+        <f t="shared" si="7"/>
+        <v>3.8000000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>104</v>
       </c>
@@ -8532,7 +8764,7 @@
         <v>323</v>
       </c>
       <c r="L63" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6</v>
       </c>
       <c r="M63" s="11"/>
@@ -8548,7 +8780,7 @@
       <c r="S63" s="11"/>
       <c r="T63" s="11"/>
       <c r="U63" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>63.4</v>
       </c>
       <c r="V63" s="4">
@@ -8556,7 +8788,7 @@
         <v>84.464999999999918</v>
       </c>
       <c r="W63" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>84.464999999999918</v>
       </c>
       <c r="X63" s="11">
@@ -8564,7 +8796,7 @@
         <v>11</v>
       </c>
       <c r="Y63" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.6677444794952692</v>
       </c>
       <c r="Z63" s="11">
@@ -8602,8 +8834,12 @@
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL63">
+        <f t="shared" si="7"/>
+        <v>25.36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>105</v>
       </c>
@@ -8636,7 +8872,7 @@
         <v>112.8</v>
       </c>
       <c r="L64" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-84.736999999999995</v>
       </c>
       <c r="M64" s="11"/>
@@ -8652,12 +8888,12 @@
       <c r="S64" s="11"/>
       <c r="T64" s="11"/>
       <c r="U64" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.6125999999999996</v>
       </c>
       <c r="V64" s="4"/>
       <c r="W64" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X64" s="11">
@@ -8665,7 +8901,7 @@
         <v>184.40870274026295</v>
       </c>
       <c r="Y64" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>184.40870274026295</v>
       </c>
       <c r="Z64" s="11">
@@ -8705,8 +8941,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL64">
+        <f t="shared" si="7"/>
+        <v>5.6125999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>107</v>
       </c>
@@ -8737,7 +8977,7 @@
         <v>416.39499999999998</v>
       </c>
       <c r="L65" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-108.71600000000001</v>
       </c>
       <c r="M65" s="11"/>
@@ -8753,7 +8993,7 @@
       <c r="S65" s="11"/>
       <c r="T65" s="11"/>
       <c r="U65" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>61.535799999999995</v>
       </c>
       <c r="V65" s="4">
@@ -8761,7 +9001,7 @@
         <v>44.937607599999858</v>
       </c>
       <c r="W65" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>44.937607599999858</v>
       </c>
       <c r="X65" s="11">
@@ -8769,7 +9009,7 @@
         <v>11</v>
       </c>
       <c r="Y65" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.269732292421649</v>
       </c>
       <c r="Z65" s="11">
@@ -8809,8 +9049,12 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL65">
+        <f t="shared" si="7"/>
+        <v>61.535799999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>109</v>
       </c>
@@ -8843,7 +9087,7 @@
         <v>1304</v>
       </c>
       <c r="L66" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-72</v>
       </c>
       <c r="M66" s="11"/>
@@ -8859,12 +9103,12 @@
       <c r="S66" s="11"/>
       <c r="T66" s="11"/>
       <c r="U66" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>246.4</v>
       </c>
       <c r="V66" s="4"/>
       <c r="W66" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X66" s="11">
@@ -8872,7 +9116,7 @@
         <v>15.023802759740258</v>
       </c>
       <c r="Y66" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.023802759740258</v>
       </c>
       <c r="Z66" s="11">
@@ -8910,8 +9154,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL66">
+        <f t="shared" si="7"/>
+        <v>98.56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>110</v>
       </c>
@@ -8944,7 +9192,7 @@
         <v>745</v>
       </c>
       <c r="L67" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-498</v>
       </c>
       <c r="M67" s="11"/>
@@ -8960,14 +9208,14 @@
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
       <c r="U67" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>49.4</v>
       </c>
       <c r="V67" s="4">
         <v>150</v>
       </c>
       <c r="W67" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="X67" s="11">
@@ -8975,7 +9223,7 @@
         <v>12.449392712550608</v>
       </c>
       <c r="Y67" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.4129554655870447</v>
       </c>
       <c r="Z67" s="11">
@@ -9013,8 +9261,12 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL67">
+        <f t="shared" si="7"/>
+        <v>19.760000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>111</v>
       </c>
@@ -9047,7 +9299,7 @@
         <v>288.95</v>
       </c>
       <c r="L68" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18.78000000000003</v>
       </c>
       <c r="M68" s="11"/>
@@ -9067,14 +9319,14 @@
       </c>
       <c r="T68" s="11"/>
       <c r="U68" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>61.546000000000006</v>
       </c>
       <c r="V68" s="4">
         <v>150</v>
       </c>
       <c r="W68" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="X68" s="11">
@@ -9082,7 +9334,7 @@
         <v>3.8293875475254224</v>
       </c>
       <c r="Y68" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3921861047021691</v>
       </c>
       <c r="Z68" s="11">
@@ -9120,8 +9372,12 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL68">
+        <f t="shared" si="7"/>
+        <v>61.546000000000006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>112</v>
       </c>
@@ -9154,7 +9410,7 @@
         <v>428.05</v>
       </c>
       <c r="L69" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.253999999999962</v>
       </c>
       <c r="M69" s="11"/>
@@ -9174,14 +9430,14 @@
       </c>
       <c r="T69" s="11"/>
       <c r="U69" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>89.860799999999998</v>
       </c>
       <c r="V69" s="4">
         <v>200</v>
       </c>
       <c r="W69" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>200</v>
       </c>
       <c r="X69" s="11">
@@ -9189,7 +9445,7 @@
         <v>2.0881518971564912</v>
       </c>
       <c r="Y69" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.13751268628812563</v>
       </c>
       <c r="Z69" s="11">
@@ -9227,8 +9483,12 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL69">
+        <f t="shared" si="7"/>
+        <v>89.860799999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>113</v>
       </c>
@@ -9261,7 +9521,7 @@
         <v>736.75</v>
       </c>
       <c r="L70" s="11">
-        <f t="shared" ref="L70:L101" si="12">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="13">E70-K70</f>
         <v>34.376999999999953</v>
       </c>
       <c r="M70" s="11"/>
@@ -9281,14 +9541,14 @@
       </c>
       <c r="T70" s="11"/>
       <c r="U70" s="11">
-        <f t="shared" ref="U70:U101" si="13">E70/5</f>
+        <f t="shared" ref="U70:U101" si="14">E70/5</f>
         <v>154.22539999999998</v>
       </c>
       <c r="V70" s="4">
         <v>350</v>
       </c>
       <c r="W70" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>350</v>
       </c>
       <c r="X70" s="11">
@@ -9296,7 +9556,7 @@
         <v>2.5396153837175977</v>
       </c>
       <c r="Y70" s="11">
-        <f t="shared" ref="Y70:Y101" si="14">(F70+O70+P70+Q70+R70+S70+T70)/U70</f>
+        <f t="shared" ref="Y70:Y101" si="15">(F70+O70+P70+Q70+R70+S70+T70)/U70</f>
         <v>0.27020969567918085</v>
       </c>
       <c r="Z70" s="11">
@@ -9334,8 +9594,12 @@
         <f t="shared" si="6"/>
         <v>350</v>
       </c>
-    </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL70">
+        <f t="shared" si="7"/>
+        <v>154.22539999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>114</v>
       </c>
@@ -9368,7 +9632,7 @@
         <v>312.10000000000002</v>
       </c>
       <c r="L71" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6.2730000000000246</v>
       </c>
       <c r="M71" s="11"/>
@@ -9384,22 +9648,22 @@
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
       <c r="U71" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>61.165399999999998</v>
       </c>
       <c r="V71" s="4">
         <v>150</v>
       </c>
       <c r="W71" s="4">
-        <f t="shared" ref="W71:W134" si="15">V71</f>
+        <f t="shared" ref="W71:W134" si="16">V71</f>
         <v>150</v>
       </c>
       <c r="X71" s="11">
-        <f t="shared" ref="X71:X134" si="16">(F71+O71+P71+Q71+R71+W71+T71+S71)/U71</f>
+        <f t="shared" ref="X71:X134" si="17">(F71+O71+P71+Q71+R71+W71+T71+S71)/U71</f>
         <v>2.8256520679992239</v>
       </c>
       <c r="Y71" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.37328520699610773</v>
       </c>
       <c r="Z71" s="11">
@@ -9434,11 +9698,15 @@
       </c>
       <c r="AJ71" s="11"/>
       <c r="AK71" s="11">
-        <f t="shared" ref="AK71:AK134" si="17">ROUND(G71*W71,0)</f>
+        <f t="shared" ref="AK71:AK134" si="18">ROUND(G71*W71,0)</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL71">
+        <f t="shared" ref="AL71:AL134" si="19">U71*G71</f>
+        <v>61.165399999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>115</v>
       </c>
@@ -9471,7 +9739,7 @@
         <v>11</v>
       </c>
       <c r="L72" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M72" s="11"/>
@@ -9485,20 +9753,20 @@
       <c r="S72" s="11"/>
       <c r="T72" s="11"/>
       <c r="U72" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="V72" s="4"/>
       <c r="W72" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X72" s="11">
+        <f t="shared" si="17"/>
+        <v>13.18181818181818</v>
+      </c>
+      <c r="Y72" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X72" s="11">
-        <f t="shared" si="16"/>
-        <v>13.18181818181818</v>
-      </c>
-      <c r="Y72" s="11">
-        <f t="shared" si="14"/>
         <v>13.18181818181818</v>
       </c>
       <c r="Z72" s="11">
@@ -9535,11 +9803,15 @@
         <v>91</v>
       </c>
       <c r="AK72" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <f t="shared" si="19"/>
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>116</v>
       </c>
@@ -9572,7 +9844,7 @@
         <v>325.7</v>
       </c>
       <c r="L73" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-26.925999999999988</v>
       </c>
       <c r="M73" s="11"/>
@@ -9586,7 +9858,7 @@
       <c r="S73" s="11"/>
       <c r="T73" s="11"/>
       <c r="U73" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>59.754800000000003</v>
       </c>
       <c r="V73" s="4">
@@ -9594,15 +9866,15 @@
         <v>103.63416620000015</v>
       </c>
       <c r="W73" s="4">
+        <f t="shared" si="16"/>
+        <v>103.63416620000015</v>
+      </c>
+      <c r="X73" s="11">
+        <f t="shared" si="17"/>
+        <v>11.000000000000002</v>
+      </c>
+      <c r="Y73" s="11">
         <f t="shared" si="15"/>
-        <v>103.63416620000015</v>
-      </c>
-      <c r="X73" s="11">
-        <f t="shared" si="16"/>
-        <v>11.000000000000002</v>
-      </c>
-      <c r="Y73" s="11">
-        <f t="shared" si="14"/>
         <v>9.2656762937872763</v>
       </c>
       <c r="Z73" s="11">
@@ -9637,11 +9909,15 @@
       </c>
       <c r="AJ73" s="11"/>
       <c r="AK73" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>104</v>
       </c>
-    </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL73">
+        <f t="shared" si="19"/>
+        <v>59.754800000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>117</v>
       </c>
@@ -9674,7 +9950,7 @@
         <v>141</v>
       </c>
       <c r="L74" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7</v>
       </c>
       <c r="M74" s="11"/>
@@ -9688,7 +9964,7 @@
       <c r="S74" s="11"/>
       <c r="T74" s="11"/>
       <c r="U74" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26.8</v>
       </c>
       <c r="V74" s="4">
@@ -9696,15 +9972,15 @@
         <v>74.299999999999983</v>
       </c>
       <c r="W74" s="4">
+        <f t="shared" si="16"/>
+        <v>74.299999999999983</v>
+      </c>
+      <c r="X74" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y74" s="11">
         <f t="shared" si="15"/>
-        <v>74.299999999999983</v>
-      </c>
-      <c r="X74" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y74" s="11">
-        <f t="shared" si="14"/>
         <v>8.2276119402985088</v>
       </c>
       <c r="Z74" s="11">
@@ -9739,11 +10015,15 @@
       </c>
       <c r="AJ74" s="11"/>
       <c r="AK74" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL74">
+        <f t="shared" si="19"/>
+        <v>16.079999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>118</v>
       </c>
@@ -9776,7 +10056,7 @@
         <v>33</v>
       </c>
       <c r="L75" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="M75" s="11"/>
@@ -9790,20 +10070,20 @@
       <c r="S75" s="11"/>
       <c r="T75" s="11"/>
       <c r="U75" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.4</v>
       </c>
       <c r="V75" s="4"/>
       <c r="W75" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X75" s="11">
+        <f t="shared" si="17"/>
+        <v>11.343749999999996</v>
+      </c>
+      <c r="Y75" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X75" s="11">
-        <f t="shared" si="16"/>
-        <v>11.343749999999996</v>
-      </c>
-      <c r="Y75" s="11">
-        <f t="shared" si="14"/>
         <v>11.343749999999996</v>
       </c>
       <c r="Z75" s="11">
@@ -9838,11 +10118,15 @@
       </c>
       <c r="AJ75" s="11"/>
       <c r="AK75" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <f t="shared" si="19"/>
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>119</v>
       </c>
@@ -9875,7 +10159,7 @@
         <v>130</v>
       </c>
       <c r="L76" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M76" s="11"/>
@@ -9889,7 +10173,7 @@
       <c r="S76" s="11"/>
       <c r="T76" s="11"/>
       <c r="U76" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.8</v>
       </c>
       <c r="V76" s="4">
@@ -9897,15 +10181,15 @@
         <v>97.6</v>
       </c>
       <c r="W76" s="4">
+        <f t="shared" si="16"/>
+        <v>97.6</v>
+      </c>
+      <c r="X76" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y76" s="11">
         <f t="shared" si="15"/>
-        <v>97.6</v>
-      </c>
-      <c r="X76" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y76" s="11">
-        <f t="shared" si="14"/>
         <v>7.0645161290322589</v>
       </c>
       <c r="Z76" s="11">
@@ -9940,11 +10224,15 @@
       </c>
       <c r="AJ76" s="11"/>
       <c r="AK76" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL76">
+        <f t="shared" si="19"/>
+        <v>9.9200000000000017</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>120</v>
       </c>
@@ -9977,7 +10265,7 @@
         <v>138</v>
       </c>
       <c r="L77" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M77" s="11"/>
@@ -9991,7 +10279,7 @@
       <c r="S77" s="11"/>
       <c r="T77" s="11"/>
       <c r="U77" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>27</v>
       </c>
       <c r="V77" s="4">
@@ -9999,15 +10287,15 @@
         <v>37.599999999999994</v>
       </c>
       <c r="W77" s="4">
+        <f t="shared" si="16"/>
+        <v>37.599999999999994</v>
+      </c>
+      <c r="X77" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y77" s="11">
         <f t="shared" si="15"/>
-        <v>37.599999999999994</v>
-      </c>
-      <c r="X77" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y77" s="11">
-        <f t="shared" si="14"/>
         <v>9.6074074074074058</v>
       </c>
       <c r="Z77" s="11">
@@ -10042,11 +10330,15 @@
       </c>
       <c r="AJ77" s="11"/>
       <c r="AK77" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL77">
+        <f t="shared" si="19"/>
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>121</v>
       </c>
@@ -10079,7 +10371,7 @@
         <v>155</v>
       </c>
       <c r="L78" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M78" s="11"/>
@@ -10093,7 +10385,7 @@
       <c r="S78" s="11"/>
       <c r="T78" s="11"/>
       <c r="U78" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>29.8</v>
       </c>
       <c r="V78" s="4">
@@ -10101,15 +10393,15 @@
         <v>38.5</v>
       </c>
       <c r="W78" s="4">
+        <f t="shared" si="16"/>
+        <v>38.5</v>
+      </c>
+      <c r="X78" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y78" s="11">
         <f t="shared" si="15"/>
-        <v>38.5</v>
-      </c>
-      <c r="X78" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y78" s="11">
-        <f t="shared" si="14"/>
         <v>9.7080536912751683</v>
       </c>
       <c r="Z78" s="11">
@@ -10144,11 +10436,15 @@
       </c>
       <c r="AJ78" s="11"/>
       <c r="AK78" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL78">
+        <f t="shared" si="19"/>
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>122</v>
       </c>
@@ -10181,7 +10477,7 @@
         <v>489</v>
       </c>
       <c r="L79" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-21</v>
       </c>
       <c r="M79" s="11"/>
@@ -10197,20 +10493,20 @@
       <c r="S79" s="11"/>
       <c r="T79" s="11"/>
       <c r="U79" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>93.6</v>
       </c>
       <c r="V79" s="4"/>
       <c r="W79" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X79" s="11">
+        <f t="shared" si="17"/>
+        <v>12.319792735042736</v>
+      </c>
+      <c r="Y79" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X79" s="11">
-        <f t="shared" si="16"/>
-        <v>12.319792735042736</v>
-      </c>
-      <c r="Y79" s="11">
-        <f t="shared" si="14"/>
         <v>12.319792735042736</v>
       </c>
       <c r="Z79" s="11">
@@ -10245,11 +10541,15 @@
       </c>
       <c r="AJ79" s="11"/>
       <c r="AK79" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <f t="shared" si="19"/>
+        <v>34.631999999999998</v>
+      </c>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>123</v>
       </c>
@@ -10282,7 +10582,7 @@
         <v>137</v>
       </c>
       <c r="L80" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M80" s="11"/>
@@ -10296,7 +10596,7 @@
       <c r="S80" s="11"/>
       <c r="T80" s="11"/>
       <c r="U80" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26.2</v>
       </c>
       <c r="V80" s="4">
@@ -10304,15 +10604,15 @@
         <v>56.000000000000028</v>
       </c>
       <c r="W80" s="4">
+        <f t="shared" si="16"/>
+        <v>56.000000000000028</v>
+      </c>
+      <c r="X80" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y80" s="11">
         <f t="shared" si="15"/>
-        <v>56.000000000000028</v>
-      </c>
-      <c r="X80" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y80" s="11">
-        <f t="shared" si="14"/>
         <v>8.8625954198473273</v>
       </c>
       <c r="Z80" s="11">
@@ -10347,11 +10647,15 @@
       </c>
       <c r="AJ80" s="11"/>
       <c r="AK80" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL80">
+        <f t="shared" si="19"/>
+        <v>15.719999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>124</v>
       </c>
@@ -10384,7 +10688,7 @@
         <v>70</v>
       </c>
       <c r="L81" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-20</v>
       </c>
       <c r="M81" s="11"/>
@@ -10398,20 +10702,20 @@
       <c r="S81" s="11"/>
       <c r="T81" s="11"/>
       <c r="U81" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
       <c r="V81" s="4"/>
       <c r="W81" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X81" s="11">
+        <f t="shared" si="17"/>
+        <v>12.72</v>
+      </c>
+      <c r="Y81" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X81" s="11">
-        <f t="shared" si="16"/>
-        <v>12.72</v>
-      </c>
-      <c r="Y81" s="11">
-        <f t="shared" si="14"/>
         <v>12.72</v>
       </c>
       <c r="Z81" s="11">
@@ -10446,11 +10750,15 @@
       </c>
       <c r="AJ81" s="11"/>
       <c r="AK81" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL81">
+        <f t="shared" si="19"/>
+        <v>3.3000000000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>125</v>
       </c>
@@ -10483,7 +10791,7 @@
         <v>301</v>
       </c>
       <c r="L82" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-14</v>
       </c>
       <c r="M82" s="11"/>
@@ -10499,7 +10807,7 @@
       <c r="S82" s="11"/>
       <c r="T82" s="11"/>
       <c r="U82" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57.4</v>
       </c>
       <c r="V82" s="4">
@@ -10507,15 +10815,15 @@
         <v>145.1930000000001</v>
       </c>
       <c r="W82" s="4">
+        <f t="shared" si="16"/>
+        <v>145.1930000000001</v>
+      </c>
+      <c r="X82" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y82" s="11">
         <f t="shared" si="15"/>
-        <v>145.1930000000001</v>
-      </c>
-      <c r="X82" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y82" s="11">
-        <f t="shared" si="14"/>
         <v>8.4705052264808351</v>
       </c>
       <c r="Z82" s="11">
@@ -10550,11 +10858,15 @@
       </c>
       <c r="AJ82" s="11"/>
       <c r="AK82" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="83" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL82">
+        <f t="shared" si="19"/>
+        <v>22.96</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>126</v>
       </c>
@@ -10587,7 +10899,7 @@
         <v>164</v>
       </c>
       <c r="L83" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-8</v>
       </c>
       <c r="M83" s="11"/>
@@ -10607,22 +10919,22 @@
       </c>
       <c r="T83" s="11"/>
       <c r="U83" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>31.2</v>
       </c>
       <c r="V83" s="4">
         <v>100</v>
       </c>
       <c r="W83" s="4">
+        <f t="shared" si="16"/>
+        <v>100</v>
+      </c>
+      <c r="X83" s="11">
+        <f t="shared" si="17"/>
+        <v>3.9285714285714284</v>
+      </c>
+      <c r="Y83" s="11">
         <f t="shared" si="15"/>
-        <v>100</v>
-      </c>
-      <c r="X83" s="11">
-        <f t="shared" si="16"/>
-        <v>3.9285714285714284</v>
-      </c>
-      <c r="Y83" s="11">
-        <f t="shared" si="14"/>
         <v>0.72344322344322343</v>
       </c>
       <c r="Z83" s="11">
@@ -10657,11 +10969,15 @@
       </c>
       <c r="AJ83" s="11"/>
       <c r="AK83" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="84" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL83">
+        <f t="shared" si="19"/>
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>127</v>
       </c>
@@ -10692,7 +11008,7 @@
         <v>177</v>
       </c>
       <c r="L84" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="M84" s="11"/>
@@ -10706,7 +11022,7 @@
       <c r="S84" s="11"/>
       <c r="T84" s="11"/>
       <c r="U84" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>35.200000000000003</v>
       </c>
       <c r="V84" s="4">
@@ -10714,15 +11030,15 @@
         <v>128.80000000000007</v>
       </c>
       <c r="W84" s="4">
+        <f t="shared" si="16"/>
+        <v>128.80000000000007</v>
+      </c>
+      <c r="X84" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y84" s="11">
         <f t="shared" si="15"/>
-        <v>128.80000000000007</v>
-      </c>
-      <c r="X84" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y84" s="11">
-        <f t="shared" si="14"/>
         <v>7.3409090909090899</v>
       </c>
       <c r="Z84" s="11">
@@ -10757,11 +11073,15 @@
       </c>
       <c r="AJ84" s="11"/>
       <c r="AK84" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="85" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL84">
+        <f t="shared" si="19"/>
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>128</v>
       </c>
@@ -10794,7 +11114,7 @@
         <v>120</v>
       </c>
       <c r="L85" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M85" s="11"/>
@@ -10808,7 +11128,7 @@
       <c r="S85" s="11"/>
       <c r="T85" s="11"/>
       <c r="U85" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="V85" s="4">
@@ -10816,15 +11136,15 @@
         <v>27</v>
       </c>
       <c r="W85" s="4">
+        <f t="shared" si="16"/>
+        <v>27</v>
+      </c>
+      <c r="X85" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y85" s="11">
         <f t="shared" si="15"/>
-        <v>27</v>
-      </c>
-      <c r="X85" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y85" s="11">
-        <f t="shared" si="14"/>
         <v>9.875</v>
       </c>
       <c r="Z85" s="11">
@@ -10859,11 +11179,15 @@
       </c>
       <c r="AJ85" s="11"/>
       <c r="AK85" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="86" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL85">
+        <f t="shared" si="19"/>
+        <v>9.6000000000000014</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>129</v>
       </c>
@@ -10894,7 +11218,7 @@
         <v>11</v>
       </c>
       <c r="L86" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.9039999999999999</v>
       </c>
       <c r="M86" s="11"/>
@@ -10908,20 +11232,20 @@
       <c r="S86" s="11"/>
       <c r="T86" s="11"/>
       <c r="U86" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.5808</v>
       </c>
       <c r="V86" s="4"/>
       <c r="W86" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X86" s="11">
+        <f t="shared" si="17"/>
+        <v>18.071915685058897</v>
+      </c>
+      <c r="Y86" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X86" s="11">
-        <f t="shared" si="16"/>
-        <v>18.071915685058897</v>
-      </c>
-      <c r="Y86" s="11">
-        <f t="shared" si="14"/>
         <v>18.071915685058897</v>
       </c>
       <c r="Z86" s="11">
@@ -10958,11 +11282,15 @@
         <v>130</v>
       </c>
       <c r="AK86" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL86">
+        <f t="shared" si="19"/>
+        <v>2.5808</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>131</v>
       </c>
@@ -10991,7 +11319,7 @@
         <v>12</v>
       </c>
       <c r="L87" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-12</v>
       </c>
       <c r="M87" s="8"/>
@@ -11005,20 +11333,20 @@
       <c r="S87" s="8"/>
       <c r="T87" s="8"/>
       <c r="U87" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V87" s="10"/>
       <c r="W87" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X87" s="11" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y87" s="11" t="e">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X87" s="11" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y87" s="11" t="e">
-        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z87" s="8">
@@ -11053,11 +11381,15 @@
       </c>
       <c r="AJ87" s="8"/>
       <c r="AK87" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL87">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>132</v>
       </c>
@@ -11090,7 +11422,7 @@
         <v>221</v>
       </c>
       <c r="L88" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.307999999999993</v>
       </c>
       <c r="M88" s="11"/>
@@ -11106,20 +11438,20 @@
       <c r="S88" s="11"/>
       <c r="T88" s="11"/>
       <c r="U88" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>46.261600000000001</v>
       </c>
       <c r="V88" s="4"/>
       <c r="W88" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X88" s="11">
+        <f t="shared" si="17"/>
+        <v>11.049023163919971</v>
+      </c>
+      <c r="Y88" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X88" s="11">
-        <f t="shared" si="16"/>
-        <v>11.049023163919971</v>
-      </c>
-      <c r="Y88" s="11">
-        <f t="shared" si="14"/>
         <v>11.049023163919971</v>
       </c>
       <c r="Z88" s="11">
@@ -11154,11 +11486,15 @@
       </c>
       <c r="AJ88" s="11"/>
       <c r="AK88" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL88">
+        <f t="shared" si="19"/>
+        <v>46.261600000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>133</v>
       </c>
@@ -11191,7 +11527,7 @@
         <v>749.67</v>
       </c>
       <c r="L89" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.3549999999999045</v>
       </c>
       <c r="M89" s="11"/>
@@ -11209,20 +11545,20 @@
       <c r="S89" s="11"/>
       <c r="T89" s="11"/>
       <c r="U89" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>149.66300000000001</v>
       </c>
       <c r="V89" s="4"/>
       <c r="W89" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X89" s="11">
+        <f t="shared" si="17"/>
+        <v>13.380323264935218</v>
+      </c>
+      <c r="Y89" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X89" s="11">
-        <f t="shared" si="16"/>
-        <v>13.380323264935218</v>
-      </c>
-      <c r="Y89" s="11">
-        <f t="shared" si="14"/>
         <v>13.380323264935218</v>
       </c>
       <c r="Z89" s="11">
@@ -11257,11 +11593,15 @@
       </c>
       <c r="AJ89" s="11"/>
       <c r="AK89" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL89">
+        <f t="shared" si="19"/>
+        <v>149.66300000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>134</v>
       </c>
@@ -11282,7 +11622,7 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M90" s="8"/>
@@ -11296,20 +11636,20 @@
       <c r="S90" s="8"/>
       <c r="T90" s="8"/>
       <c r="U90" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V90" s="10"/>
       <c r="W90" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X90" s="11" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y90" s="11" t="e">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X90" s="11" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y90" s="11" t="e">
-        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z90" s="8">
@@ -11346,11 +11686,15 @@
         <v>45</v>
       </c>
       <c r="AK90" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL90">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>135</v>
       </c>
@@ -11383,7 +11727,7 @@
         <v>1992.866</v>
       </c>
       <c r="L91" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.6469999999999345</v>
       </c>
       <c r="M91" s="11"/>
@@ -11401,20 +11745,20 @@
       <c r="S91" s="11"/>
       <c r="T91" s="11"/>
       <c r="U91" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>398.24380000000002</v>
       </c>
       <c r="V91" s="4"/>
       <c r="W91" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X91" s="11">
+        <f t="shared" si="17"/>
+        <v>15.597267670206039</v>
+      </c>
+      <c r="Y91" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X91" s="11">
-        <f t="shared" si="16"/>
-        <v>15.597267670206039</v>
-      </c>
-      <c r="Y91" s="11">
-        <f t="shared" si="14"/>
         <v>15.597267670206039</v>
       </c>
       <c r="Z91" s="11">
@@ -11449,11 +11793,15 @@
       </c>
       <c r="AJ91" s="11"/>
       <c r="AK91" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL91">
+        <f t="shared" si="19"/>
+        <v>398.24380000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>136</v>
       </c>
@@ -11486,7 +11834,7 @@
         <v>1921.75</v>
       </c>
       <c r="L92" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34.942000000000007</v>
       </c>
       <c r="M92" s="11"/>
@@ -11504,20 +11852,20 @@
       <c r="S92" s="11"/>
       <c r="T92" s="11"/>
       <c r="U92" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>377.36160000000001</v>
       </c>
       <c r="V92" s="4"/>
       <c r="W92" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X92" s="11">
+        <f t="shared" si="17"/>
+        <v>16.33775813490297</v>
+      </c>
+      <c r="Y92" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X92" s="11">
-        <f t="shared" si="16"/>
-        <v>16.33775813490297</v>
-      </c>
-      <c r="Y92" s="11">
-        <f t="shared" si="14"/>
         <v>16.33775813490297</v>
       </c>
       <c r="Z92" s="11">
@@ -11552,11 +11900,15 @@
       </c>
       <c r="AJ92" s="11"/>
       <c r="AK92" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL92">
+        <f t="shared" si="19"/>
+        <v>377.36160000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>137</v>
       </c>
@@ -11589,7 +11941,7 @@
         <v>2478.5500000000002</v>
       </c>
       <c r="L93" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-40.648000000000138</v>
       </c>
       <c r="M93" s="11"/>
@@ -11609,20 +11961,20 @@
         <v>400</v>
       </c>
       <c r="U93" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>487.5804</v>
       </c>
       <c r="V93" s="4"/>
       <c r="W93" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X93" s="11">
+        <f t="shared" si="17"/>
+        <v>17.227740895245176</v>
+      </c>
+      <c r="Y93" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X93" s="11">
-        <f t="shared" si="16"/>
-        <v>17.227740895245176</v>
-      </c>
-      <c r="Y93" s="11">
-        <f t="shared" si="14"/>
         <v>17.227740895245176</v>
       </c>
       <c r="Z93" s="11">
@@ -11657,11 +12009,15 @@
       </c>
       <c r="AJ93" s="11"/>
       <c r="AK93" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL93">
+        <f t="shared" si="19"/>
+        <v>487.5804</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>138</v>
       </c>
@@ -11694,7 +12050,7 @@
         <v>44.6</v>
       </c>
       <c r="L94" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.2000000000000028</v>
       </c>
       <c r="M94" s="11"/>
@@ -11708,7 +12064,7 @@
       <c r="S94" s="11"/>
       <c r="T94" s="11"/>
       <c r="U94" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.48</v>
       </c>
       <c r="V94" s="4">
@@ -11716,15 +12072,15 @@
         <v>43.897000000000013</v>
       </c>
       <c r="W94" s="4">
+        <f t="shared" si="16"/>
+        <v>43.897000000000013</v>
+      </c>
+      <c r="X94" s="11">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="Y94" s="11">
         <f t="shared" si="15"/>
-        <v>43.897000000000013</v>
-      </c>
-      <c r="X94" s="11">
-        <f t="shared" si="16"/>
-        <v>10</v>
-      </c>
-      <c r="Y94" s="11">
-        <f t="shared" si="14"/>
         <v>4.8234669811320749</v>
       </c>
       <c r="Z94" s="11">
@@ -11759,11 +12115,15 @@
       </c>
       <c r="AJ94" s="11"/>
       <c r="AK94" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="95" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL94">
+        <f t="shared" si="19"/>
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>139</v>
       </c>
@@ -11792,7 +12152,7 @@
         <v>5.2</v>
       </c>
       <c r="L95" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.2</v>
       </c>
       <c r="M95" s="8"/>
@@ -11806,20 +12166,20 @@
       <c r="S95" s="8"/>
       <c r="T95" s="8"/>
       <c r="U95" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V95" s="10"/>
       <c r="W95" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X95" s="11" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y95" s="11" t="e">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X95" s="11" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y95" s="11" t="e">
-        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z95" s="8">
@@ -11854,11 +12214,15 @@
       </c>
       <c r="AJ95" s="8"/>
       <c r="AK95" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL95">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>140</v>
       </c>
@@ -11889,7 +12253,7 @@
         <v>7</v>
       </c>
       <c r="L96" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-16</v>
       </c>
       <c r="M96" s="11"/>
@@ -11909,22 +12273,22 @@
       </c>
       <c r="T96" s="11"/>
       <c r="U96" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-1.8</v>
       </c>
       <c r="V96" s="4">
         <v>100</v>
       </c>
       <c r="W96" s="4">
+        <f t="shared" si="16"/>
+        <v>100</v>
+      </c>
+      <c r="X96" s="11">
+        <f t="shared" si="17"/>
+        <v>-47.592592592592588</v>
+      </c>
+      <c r="Y96" s="11">
         <f t="shared" si="15"/>
-        <v>100</v>
-      </c>
-      <c r="X96" s="11">
-        <f t="shared" si="16"/>
-        <v>-47.592592592592588</v>
-      </c>
-      <c r="Y96" s="11">
-        <f t="shared" si="14"/>
         <v>7.9629629629629637</v>
       </c>
       <c r="Z96" s="11">
@@ -11959,11 +12323,15 @@
       </c>
       <c r="AJ96" s="11"/>
       <c r="AK96" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL96">
+        <f t="shared" si="19"/>
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>141</v>
       </c>
@@ -11996,7 +12364,7 @@
         <v>249</v>
       </c>
       <c r="L97" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M97" s="11"/>
@@ -12010,7 +12378,7 @@
       <c r="S97" s="11"/>
       <c r="T97" s="11"/>
       <c r="U97" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>49</v>
       </c>
       <c r="V97" s="4">
@@ -12018,15 +12386,15 @@
         <v>107.75000000000011</v>
       </c>
       <c r="W97" s="4">
+        <f t="shared" si="16"/>
+        <v>107.75000000000011</v>
+      </c>
+      <c r="X97" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y97" s="11">
         <f t="shared" si="15"/>
-        <v>107.75000000000011</v>
-      </c>
-      <c r="X97" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y97" s="11">
-        <f t="shared" si="14"/>
         <v>8.8010204081632626</v>
       </c>
       <c r="Z97" s="11">
@@ -12061,11 +12429,15 @@
       </c>
       <c r="AJ97" s="11"/>
       <c r="AK97" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL97">
+        <f t="shared" si="19"/>
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>142</v>
       </c>
@@ -12086,7 +12458,7 @@
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
       <c r="L98" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M98" s="8"/>
@@ -12100,20 +12472,20 @@
       <c r="S98" s="8"/>
       <c r="T98" s="8"/>
       <c r="U98" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V98" s="10"/>
       <c r="W98" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X98" s="11" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y98" s="11" t="e">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X98" s="11" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y98" s="11" t="e">
-        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z98" s="8">
@@ -12150,11 +12522,15 @@
         <v>45</v>
       </c>
       <c r="AK98" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL98">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>143</v>
       </c>
@@ -12187,7 +12563,7 @@
         <v>58</v>
       </c>
       <c r="L99" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-38</v>
       </c>
       <c r="M99" s="11"/>
@@ -12205,22 +12581,22 @@
       </c>
       <c r="T99" s="11"/>
       <c r="U99" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="V99" s="4">
         <v>50</v>
       </c>
       <c r="W99" s="4">
+        <f t="shared" si="16"/>
+        <v>50</v>
+      </c>
+      <c r="X99" s="11">
+        <f t="shared" si="17"/>
+        <v>56.642857142857146</v>
+      </c>
+      <c r="Y99" s="11">
         <f t="shared" si="15"/>
-        <v>50</v>
-      </c>
-      <c r="X99" s="11">
-        <f t="shared" si="16"/>
-        <v>56.642857142857146</v>
-      </c>
-      <c r="Y99" s="11">
-        <f t="shared" si="14"/>
         <v>44.142857142857146</v>
       </c>
       <c r="Z99" s="11">
@@ -12255,11 +12631,15 @@
       </c>
       <c r="AJ99" s="11"/>
       <c r="AK99" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL99">
+        <f t="shared" si="19"/>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>144</v>
       </c>
@@ -12292,7 +12672,7 @@
         <v>186</v>
       </c>
       <c r="L100" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M100" s="11"/>
@@ -12308,7 +12688,7 @@
       <c r="S100" s="11"/>
       <c r="T100" s="11"/>
       <c r="U100" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36.6</v>
       </c>
       <c r="V100" s="4">
@@ -12316,15 +12696,15 @@
         <v>26.088000000000193</v>
       </c>
       <c r="W100" s="4">
+        <f t="shared" si="16"/>
+        <v>26.088000000000193</v>
+      </c>
+      <c r="X100" s="11">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="Y100" s="11">
         <f t="shared" si="15"/>
-        <v>26.088000000000193</v>
-      </c>
-      <c r="X100" s="11">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="Y100" s="11">
-        <f t="shared" si="14"/>
         <v>10.287213114754094</v>
       </c>
       <c r="Z100" s="11">
@@ -12359,11 +12739,15 @@
       </c>
       <c r="AJ100" s="11"/>
       <c r="AK100" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL100">
+        <f t="shared" si="19"/>
+        <v>2.5620000000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>145</v>
       </c>
@@ -12394,7 +12778,7 @@
         <v>39</v>
       </c>
       <c r="L101" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-40</v>
       </c>
       <c r="M101" s="8"/>
@@ -12408,20 +12792,20 @@
       <c r="S101" s="8"/>
       <c r="T101" s="8"/>
       <c r="U101" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
       <c r="V101" s="10"/>
       <c r="W101" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X101" s="11">
+        <f t="shared" si="17"/>
+        <v>-10</v>
+      </c>
+      <c r="Y101" s="11">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X101" s="11">
-        <f t="shared" si="16"/>
-        <v>-10</v>
-      </c>
-      <c r="Y101" s="11">
-        <f t="shared" si="14"/>
         <v>-10</v>
       </c>
       <c r="Z101" s="8">
@@ -12456,11 +12840,15 @@
       </c>
       <c r="AJ101" s="8"/>
       <c r="AK101" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL101">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
         <v>146</v>
       </c>
@@ -12493,7 +12881,7 @@
         <v>203</v>
       </c>
       <c r="L102" s="11">
-        <f t="shared" ref="L102:L133" si="18">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="20">E102-K102</f>
         <v>-12</v>
       </c>
       <c r="M102" s="11"/>
@@ -12509,22 +12897,22 @@
       <c r="S102" s="11"/>
       <c r="T102" s="11"/>
       <c r="U102" s="11">
-        <f t="shared" ref="U102:U134" si="19">E102/5</f>
+        <f t="shared" ref="U102:U134" si="21">E102/5</f>
         <v>38.200000000000003</v>
       </c>
       <c r="V102" s="4">
         <v>100</v>
       </c>
       <c r="W102" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="X102" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.9685863874345539</v>
       </c>
       <c r="Y102" s="11">
-        <f t="shared" ref="Y102:Y134" si="20">(F102+O102+P102+Q102+R102+S102+T102)/U102</f>
+        <f t="shared" ref="Y102:Y134" si="22">(F102+O102+P102+Q102+R102+S102+T102)/U102</f>
         <v>0.3507853403141355</v>
       </c>
       <c r="Z102" s="11">
@@ -12559,11 +12947,15 @@
       </c>
       <c r="AJ102" s="11"/>
       <c r="AK102" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL102">
+        <f t="shared" si="19"/>
+        <v>11.46</v>
+      </c>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>147</v>
       </c>
@@ -12596,7 +12988,7 @@
         <v>113.2</v>
       </c>
       <c r="L103" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-4.5050000000000097</v>
       </c>
       <c r="M103" s="11"/>
@@ -12614,7 +13006,7 @@
       </c>
       <c r="T103" s="11"/>
       <c r="U103" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>21.738999999999997</v>
       </c>
       <c r="V103" s="4">
@@ -12622,15 +13014,15 @@
         <v>83.268999999999963</v>
       </c>
       <c r="W103" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>83.268999999999963</v>
       </c>
       <c r="X103" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y103" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>7.1696030176181074</v>
       </c>
       <c r="Z103" s="11">
@@ -12665,11 +13057,15 @@
       </c>
       <c r="AJ103" s="11"/>
       <c r="AK103" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>83</v>
       </c>
-    </row>
-    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL103">
+        <f t="shared" si="19"/>
+        <v>21.738999999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>148</v>
       </c>
@@ -12690,7 +13086,7 @@
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
       <c r="L104" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M104" s="8"/>
@@ -12704,20 +13100,20 @@
       <c r="S104" s="8"/>
       <c r="T104" s="8"/>
       <c r="U104" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V104" s="10"/>
       <c r="W104" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X104" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y104" s="11" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z104" s="8">
@@ -12754,11 +13150,15 @@
         <v>45</v>
       </c>
       <c r="AK104" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL104">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>149</v>
       </c>
@@ -12789,7 +13189,7 @@
         <v>20</v>
       </c>
       <c r="L105" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-8</v>
       </c>
       <c r="M105" s="11"/>
@@ -12805,22 +13205,22 @@
       <c r="S105" s="11"/>
       <c r="T105" s="11"/>
       <c r="U105" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.4</v>
       </c>
       <c r="V105" s="4">
         <v>20</v>
       </c>
       <c r="W105" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="X105" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.9166666666666679</v>
       </c>
       <c r="Y105" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1.4166666666666661</v>
       </c>
       <c r="Z105" s="11">
@@ -12857,11 +13257,15 @@
         <v>150</v>
       </c>
       <c r="AK105" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL105">
+        <f t="shared" si="19"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>151</v>
       </c>
@@ -12894,7 +13298,7 @@
         <v>293</v>
       </c>
       <c r="L106" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-6</v>
       </c>
       <c r="M106" s="11"/>
@@ -12908,7 +13312,7 @@
       <c r="S106" s="11"/>
       <c r="T106" s="11"/>
       <c r="U106" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>57.4</v>
       </c>
       <c r="V106" s="4">
@@ -12916,15 +13320,15 @@
         <v>151.12440000000026</v>
       </c>
       <c r="W106" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>151.12440000000026</v>
       </c>
       <c r="X106" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y106" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.3671707317073114</v>
       </c>
       <c r="Z106" s="11">
@@ -12959,11 +13363,15 @@
       </c>
       <c r="AJ106" s="11"/>
       <c r="AK106" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL106">
+        <f t="shared" si="19"/>
+        <v>4.5919999999999996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>152</v>
       </c>
@@ -12996,7 +13404,7 @@
         <v>278</v>
       </c>
       <c r="L107" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-7</v>
       </c>
       <c r="M107" s="11"/>
@@ -13010,7 +13418,7 @@
       <c r="S107" s="11"/>
       <c r="T107" s="11"/>
       <c r="U107" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>54.2</v>
       </c>
       <c r="V107" s="4">
@@ -13018,15 +13426,15 @@
         <v>199.21500000000003</v>
       </c>
       <c r="W107" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>199.21500000000003</v>
       </c>
       <c r="X107" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y107" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>7.3244464944649446</v>
       </c>
       <c r="Z107" s="11">
@@ -13061,11 +13469,15 @@
       </c>
       <c r="AJ107" s="11"/>
       <c r="AK107" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL107">
+        <f t="shared" si="19"/>
+        <v>4.3360000000000003</v>
+      </c>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>153</v>
       </c>
@@ -13096,7 +13508,7 @@
         <v>7</v>
       </c>
       <c r="L108" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M108" s="11"/>
@@ -13110,7 +13522,7 @@
       <c r="S108" s="11"/>
       <c r="T108" s="11"/>
       <c r="U108" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.4</v>
       </c>
       <c r="V108" s="4">
@@ -13118,15 +13530,15 @@
         <v>4.1999999999999957</v>
       </c>
       <c r="W108" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.1999999999999957</v>
       </c>
       <c r="X108" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y108" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.0000000000000018</v>
       </c>
       <c r="Z108" s="11">
@@ -13163,11 +13575,15 @@
         <v>154</v>
       </c>
       <c r="AK108" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL108">
+        <f t="shared" si="19"/>
+        <v>0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>155</v>
       </c>
@@ -13200,7 +13616,7 @@
         <v>540.02499999999998</v>
       </c>
       <c r="L109" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-135.26299999999998</v>
       </c>
       <c r="M109" s="11"/>
@@ -13218,61 +13634,65 @@
       <c r="S109" s="11"/>
       <c r="T109" s="11"/>
       <c r="U109" s="11">
+        <f t="shared" si="21"/>
+        <v>80.952399999999997</v>
+      </c>
+      <c r="V109" s="4">
+        <v>250</v>
+      </c>
+      <c r="W109" s="4">
+        <f t="shared" si="16"/>
+        <v>250</v>
+      </c>
+      <c r="X109" s="11">
+        <f t="shared" si="17"/>
+        <v>4.3327807452280602</v>
+      </c>
+      <c r="Y109" s="11">
+        <f t="shared" si="22"/>
+        <v>1.2445461777538405</v>
+      </c>
+      <c r="Z109" s="11">
+        <v>96.791799999999995</v>
+      </c>
+      <c r="AA109" s="11">
+        <v>97.415999999999997</v>
+      </c>
+      <c r="AB109" s="11">
+        <v>88.752200000000002</v>
+      </c>
+      <c r="AC109" s="11">
+        <v>85.401199999999989</v>
+      </c>
+      <c r="AD109" s="11">
+        <v>87.400199999999998</v>
+      </c>
+      <c r="AE109" s="11">
+        <v>80.573400000000007</v>
+      </c>
+      <c r="AF109" s="11">
+        <v>83.3596</v>
+      </c>
+      <c r="AG109" s="11">
+        <v>84.740200000000002</v>
+      </c>
+      <c r="AH109" s="11">
+        <v>85.5518</v>
+      </c>
+      <c r="AI109" s="11">
+        <v>88.798400000000001</v>
+      </c>
+      <c r="AJ109" s="11"/>
+      <c r="AK109" s="11">
+        <f t="shared" si="18"/>
+        <v>250</v>
+      </c>
+      <c r="AL109">
         <f t="shared" si="19"/>
         <v>80.952399999999997</v>
       </c>
-      <c r="V109" s="4">
-        <v>250</v>
-      </c>
-      <c r="W109" s="4">
-        <f t="shared" si="15"/>
-        <v>250</v>
-      </c>
-      <c r="X109" s="11">
-        <f t="shared" si="16"/>
-        <v>4.3327807452280602</v>
-      </c>
-      <c r="Y109" s="11">
-        <f t="shared" si="20"/>
-        <v>1.2445461777538405</v>
-      </c>
-      <c r="Z109" s="11">
-        <v>96.791799999999995</v>
-      </c>
-      <c r="AA109" s="11">
-        <v>97.415999999999997</v>
-      </c>
-      <c r="AB109" s="11">
-        <v>88.752200000000002</v>
-      </c>
-      <c r="AC109" s="11">
-        <v>85.401199999999989</v>
-      </c>
-      <c r="AD109" s="11">
-        <v>87.400199999999998</v>
-      </c>
-      <c r="AE109" s="11">
-        <v>80.573400000000007</v>
-      </c>
-      <c r="AF109" s="11">
-        <v>83.3596</v>
-      </c>
-      <c r="AG109" s="11">
-        <v>84.740200000000002</v>
-      </c>
-      <c r="AH109" s="11">
-        <v>85.5518</v>
-      </c>
-      <c r="AI109" s="11">
-        <v>88.798400000000001</v>
-      </c>
-      <c r="AJ109" s="11"/>
-      <c r="AK109" s="11">
-        <f t="shared" si="17"/>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>156</v>
       </c>
@@ -13305,7 +13725,7 @@
         <v>190.8</v>
       </c>
       <c r="L110" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-55.472000000000008</v>
       </c>
       <c r="M110" s="11"/>
@@ -13323,61 +13743,65 @@
       </c>
       <c r="T110" s="11"/>
       <c r="U110" s="11">
+        <f t="shared" si="21"/>
+        <v>27.0656</v>
+      </c>
+      <c r="V110" s="4">
+        <v>150</v>
+      </c>
+      <c r="W110" s="4">
+        <f t="shared" si="16"/>
+        <v>150</v>
+      </c>
+      <c r="X110" s="11">
+        <f t="shared" si="17"/>
+        <v>18.324810829983448</v>
+      </c>
+      <c r="Y110" s="11">
+        <f t="shared" si="22"/>
+        <v>12.782720501300544</v>
+      </c>
+      <c r="Z110" s="11">
+        <v>78.425399999999996</v>
+      </c>
+      <c r="AA110" s="11">
+        <v>77.138599999999997</v>
+      </c>
+      <c r="AB110" s="11">
+        <v>61.042400000000001</v>
+      </c>
+      <c r="AC110" s="11">
+        <v>57.488399999999999</v>
+      </c>
+      <c r="AD110" s="11">
+        <v>60.191400000000002</v>
+      </c>
+      <c r="AE110" s="11">
+        <v>58.831200000000003</v>
+      </c>
+      <c r="AF110" s="11">
+        <v>66.663600000000002</v>
+      </c>
+      <c r="AG110" s="11">
+        <v>64.051199999999994</v>
+      </c>
+      <c r="AH110" s="11">
+        <v>58.3504</v>
+      </c>
+      <c r="AI110" s="11">
+        <v>61.6798</v>
+      </c>
+      <c r="AJ110" s="11"/>
+      <c r="AK110" s="11">
+        <f t="shared" si="18"/>
+        <v>150</v>
+      </c>
+      <c r="AL110">
         <f t="shared" si="19"/>
         <v>27.0656</v>
       </c>
-      <c r="V110" s="4">
-        <v>150</v>
-      </c>
-      <c r="W110" s="4">
-        <f t="shared" si="15"/>
-        <v>150</v>
-      </c>
-      <c r="X110" s="11">
-        <f t="shared" si="16"/>
-        <v>18.324810829983448</v>
-      </c>
-      <c r="Y110" s="11">
-        <f t="shared" si="20"/>
-        <v>12.782720501300544</v>
-      </c>
-      <c r="Z110" s="11">
-        <v>78.425399999999996</v>
-      </c>
-      <c r="AA110" s="11">
-        <v>77.138599999999997</v>
-      </c>
-      <c r="AB110" s="11">
-        <v>61.042400000000001</v>
-      </c>
-      <c r="AC110" s="11">
-        <v>57.488399999999999</v>
-      </c>
-      <c r="AD110" s="11">
-        <v>60.191400000000002</v>
-      </c>
-      <c r="AE110" s="11">
-        <v>58.831200000000003</v>
-      </c>
-      <c r="AF110" s="11">
-        <v>66.663600000000002</v>
-      </c>
-      <c r="AG110" s="11">
-        <v>64.051199999999994</v>
-      </c>
-      <c r="AH110" s="11">
-        <v>58.3504</v>
-      </c>
-      <c r="AI110" s="11">
-        <v>61.6798</v>
-      </c>
-      <c r="AJ110" s="11"/>
-      <c r="AK110" s="11">
-        <f t="shared" si="17"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>99</v>
       </c>
@@ -13410,7 +13834,7 @@
         <v>252.8</v>
       </c>
       <c r="L111" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-60.513000000000005</v>
       </c>
       <c r="M111" s="11"/>
@@ -13430,61 +13854,65 @@
       </c>
       <c r="T111" s="11"/>
       <c r="U111" s="11">
+        <f t="shared" si="21"/>
+        <v>38.4574</v>
+      </c>
+      <c r="V111" s="4">
+        <v>200</v>
+      </c>
+      <c r="W111" s="4">
+        <f t="shared" si="16"/>
+        <v>200</v>
+      </c>
+      <c r="X111" s="11">
+        <f t="shared" si="17"/>
+        <v>4.4984840368823686</v>
+      </c>
+      <c r="Y111" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.70207554332846211</v>
+      </c>
+      <c r="Z111" s="11">
+        <v>90.9636</v>
+      </c>
+      <c r="AA111" s="11">
+        <v>99.641199999999998</v>
+      </c>
+      <c r="AB111" s="11">
+        <v>90.812600000000003</v>
+      </c>
+      <c r="AC111" s="11">
+        <v>87.560400000000001</v>
+      </c>
+      <c r="AD111" s="11">
+        <v>101.8978</v>
+      </c>
+      <c r="AE111" s="11">
+        <v>89.504600000000011</v>
+      </c>
+      <c r="AF111" s="11">
+        <v>76.044000000000011</v>
+      </c>
+      <c r="AG111" s="11">
+        <v>82.587199999999996</v>
+      </c>
+      <c r="AH111" s="11">
+        <v>93.196200000000005</v>
+      </c>
+      <c r="AI111" s="11">
+        <v>104.8322</v>
+      </c>
+      <c r="AJ111" s="11"/>
+      <c r="AK111" s="11">
+        <f t="shared" si="18"/>
+        <v>200</v>
+      </c>
+      <c r="AL111">
         <f t="shared" si="19"/>
         <v>38.4574</v>
       </c>
-      <c r="V111" s="4">
-        <v>200</v>
-      </c>
-      <c r="W111" s="4">
-        <f t="shared" si="15"/>
-        <v>200</v>
-      </c>
-      <c r="X111" s="11">
-        <f t="shared" si="16"/>
-        <v>4.4984840368823686</v>
-      </c>
-      <c r="Y111" s="11">
-        <f t="shared" si="20"/>
-        <v>-0.70207554332846211</v>
-      </c>
-      <c r="Z111" s="11">
-        <v>90.9636</v>
-      </c>
-      <c r="AA111" s="11">
-        <v>99.641199999999998</v>
-      </c>
-      <c r="AB111" s="11">
-        <v>90.812600000000003</v>
-      </c>
-      <c r="AC111" s="11">
-        <v>87.560400000000001</v>
-      </c>
-      <c r="AD111" s="11">
-        <v>101.8978</v>
-      </c>
-      <c r="AE111" s="11">
-        <v>89.504600000000011</v>
-      </c>
-      <c r="AF111" s="11">
-        <v>76.044000000000011</v>
-      </c>
-      <c r="AG111" s="11">
-        <v>82.587199999999996</v>
-      </c>
-      <c r="AH111" s="11">
-        <v>93.196200000000005</v>
-      </c>
-      <c r="AI111" s="11">
-        <v>104.8322</v>
-      </c>
-      <c r="AJ111" s="11"/>
-      <c r="AK111" s="11">
-        <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>157</v>
       </c>
@@ -13505,7 +13933,7 @@
       <c r="J112" s="8"/>
       <c r="K112" s="8"/>
       <c r="L112" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M112" s="8"/>
@@ -13519,20 +13947,20 @@
       <c r="S112" s="8"/>
       <c r="T112" s="8"/>
       <c r="U112" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V112" s="10"/>
       <c r="W112" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X112" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y112" s="11" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z112" s="8">
@@ -13569,11 +13997,15 @@
         <v>45</v>
       </c>
       <c r="AK112" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL112">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>158</v>
       </c>
@@ -13604,7 +14036,7 @@
         <v>3.9</v>
       </c>
       <c r="L113" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-1.0699999999999998</v>
       </c>
       <c r="M113" s="11"/>
@@ -13618,61 +14050,65 @@
       <c r="S113" s="11"/>
       <c r="T113" s="11"/>
       <c r="U113" s="11">
+        <f t="shared" si="21"/>
+        <v>0.56600000000000006</v>
+      </c>
+      <c r="V113" s="4"/>
+      <c r="W113" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X113" s="11">
+        <f t="shared" si="17"/>
+        <v>16.044169611307417</v>
+      </c>
+      <c r="Y113" s="11">
+        <f t="shared" si="22"/>
+        <v>16.044169611307417</v>
+      </c>
+      <c r="Z113" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="11">
+        <v>0.26879999999999998</v>
+      </c>
+      <c r="AB113" s="11">
+        <v>0.54180000000000006</v>
+      </c>
+      <c r="AC113" s="11">
+        <v>0.54720000000000002</v>
+      </c>
+      <c r="AD113" s="11">
+        <v>1.615</v>
+      </c>
+      <c r="AE113" s="11">
+        <v>1.3408</v>
+      </c>
+      <c r="AF113" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG113" s="11">
+        <v>1.2816000000000001</v>
+      </c>
+      <c r="AH113" s="11">
+        <v>0.28160000000000002</v>
+      </c>
+      <c r="AI113" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ113" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="AK113" s="11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL113">
         <f t="shared" si="19"/>
         <v>0.56600000000000006</v>
       </c>
-      <c r="V113" s="4"/>
-      <c r="W113" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X113" s="11">
-        <f t="shared" si="16"/>
-        <v>16.044169611307417</v>
-      </c>
-      <c r="Y113" s="11">
-        <f t="shared" si="20"/>
-        <v>16.044169611307417</v>
-      </c>
-      <c r="Z113" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA113" s="11">
-        <v>0.26879999999999998</v>
-      </c>
-      <c r="AB113" s="11">
-        <v>0.54180000000000006</v>
-      </c>
-      <c r="AC113" s="11">
-        <v>0.54720000000000002</v>
-      </c>
-      <c r="AD113" s="11">
-        <v>1.615</v>
-      </c>
-      <c r="AE113" s="11">
-        <v>1.3408</v>
-      </c>
-      <c r="AF113" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG113" s="11">
-        <v>1.2816000000000001</v>
-      </c>
-      <c r="AH113" s="11">
-        <v>0.28160000000000002</v>
-      </c>
-      <c r="AI113" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ113" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="AK113" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>160</v>
       </c>
@@ -13705,7 +14141,7 @@
         <v>420</v>
       </c>
       <c r="L114" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-203</v>
       </c>
       <c r="M114" s="11"/>
@@ -13723,7 +14159,7 @@
       <c r="S114" s="11"/>
       <c r="T114" s="11"/>
       <c r="U114" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>43.4</v>
       </c>
       <c r="V114" s="4">
@@ -13731,15 +14167,15 @@
         <v>188.15500000000009</v>
       </c>
       <c r="W114" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>188.15500000000009</v>
       </c>
       <c r="X114" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y114" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.6646313364055274</v>
       </c>
       <c r="Z114" s="11">
@@ -13774,11 +14210,15 @@
       </c>
       <c r="AJ114" s="11"/>
       <c r="AK114" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>53</v>
       </c>
-    </row>
-    <row r="115" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL114">
+        <f t="shared" si="19"/>
+        <v>12.152000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>161</v>
       </c>
@@ -13799,7 +14239,7 @@
       <c r="J115" s="8"/>
       <c r="K115" s="8"/>
       <c r="L115" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M115" s="8"/>
@@ -13813,20 +14253,20 @@
       <c r="S115" s="8"/>
       <c r="T115" s="8"/>
       <c r="U115" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V115" s="10"/>
       <c r="W115" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X115" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y115" s="11" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z115" s="8">
@@ -13863,11 +14303,15 @@
         <v>45</v>
       </c>
       <c r="AK115" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL115">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>162</v>
       </c>
@@ -13900,7 +14344,7 @@
         <v>395</v>
       </c>
       <c r="L116" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-164</v>
       </c>
       <c r="M116" s="11"/>
@@ -13920,22 +14364,22 @@
       </c>
       <c r="T116" s="11"/>
       <c r="U116" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>46.2</v>
       </c>
       <c r="V116" s="4">
         <v>200</v>
       </c>
       <c r="W116" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>200</v>
       </c>
       <c r="X116" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.0822510822510845</v>
       </c>
       <c r="Y116" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.7532467532467562</v>
       </c>
       <c r="Z116" s="11">
@@ -13970,11 +14414,15 @@
       </c>
       <c r="AJ116" s="11"/>
       <c r="AK116" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>56</v>
       </c>
-    </row>
-    <row r="117" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL116">
+        <f t="shared" si="19"/>
+        <v>12.936000000000002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>163</v>
       </c>
@@ -14005,7 +14453,7 @@
         <v>101</v>
       </c>
       <c r="L117" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-38</v>
       </c>
       <c r="M117" s="11"/>
@@ -14019,7 +14467,7 @@
       <c r="S117" s="11"/>
       <c r="T117" s="11"/>
       <c r="U117" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.6</v>
       </c>
       <c r="V117" s="4">
@@ -14027,15 +14475,15 @@
         <v>77.8</v>
       </c>
       <c r="W117" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>77.8</v>
       </c>
       <c r="X117" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8</v>
       </c>
       <c r="Y117" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.8253968253968254</v>
       </c>
       <c r="Z117" s="11">
@@ -14072,11 +14520,15 @@
         <v>164</v>
       </c>
       <c r="AK117" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="118" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL117">
+        <f t="shared" si="19"/>
+        <v>1.1339999999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>165</v>
       </c>
@@ -14107,7 +14559,7 @@
         <v>232.85</v>
       </c>
       <c r="L118" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-16.153999999999996</v>
       </c>
       <c r="M118" s="11"/>
@@ -14121,7 +14573,7 @@
       <c r="S118" s="11"/>
       <c r="T118" s="11"/>
       <c r="U118" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>43.339199999999998</v>
       </c>
       <c r="V118" s="4">
@@ -14129,15 +14581,15 @@
         <v>246.79639999999995</v>
       </c>
       <c r="W118" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>246.79639999999995</v>
       </c>
       <c r="X118" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8</v>
       </c>
       <c r="Y118" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.3054694133717288</v>
       </c>
       <c r="Z118" s="11">
@@ -14172,11 +14624,15 @@
       </c>
       <c r="AJ118" s="11"/>
       <c r="AK118" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>247</v>
       </c>
-    </row>
-    <row r="119" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL118">
+        <f t="shared" si="19"/>
+        <v>43.339199999999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>166</v>
       </c>
@@ -14207,7 +14663,7 @@
         <v>42.5</v>
       </c>
       <c r="L119" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-43.677999999999997</v>
       </c>
       <c r="M119" s="11"/>
@@ -14221,61 +14677,65 @@
       <c r="S119" s="11"/>
       <c r="T119" s="11"/>
       <c r="U119" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.23559999999999998</v>
+      </c>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X119" s="11">
+        <f t="shared" si="17"/>
+        <v>-348.42954159592534</v>
+      </c>
+      <c r="Y119" s="11">
+        <f t="shared" si="22"/>
+        <v>-348.42954159592534</v>
+      </c>
+      <c r="Z119" s="11">
+        <v>-0.3604</v>
+      </c>
+      <c r="AA119" s="11">
+        <v>-0.12479999999999999</v>
+      </c>
+      <c r="AB119" s="11">
+        <v>-0.17460000000000001</v>
+      </c>
+      <c r="AC119" s="11">
+        <v>-0.35780000000000001</v>
+      </c>
+      <c r="AD119" s="11">
+        <v>-0.1832</v>
+      </c>
+      <c r="AE119" s="11">
+        <v>0.36159999999999998</v>
+      </c>
+      <c r="AF119" s="11">
+        <v>4.1176000000000004</v>
+      </c>
+      <c r="AG119" s="11">
+        <v>5.7633999999999999</v>
+      </c>
+      <c r="AH119" s="11">
+        <v>15.0108</v>
+      </c>
+      <c r="AI119" s="11">
+        <v>18.382400000000001</v>
+      </c>
+      <c r="AJ119" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK119" s="11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL119">
         <f t="shared" si="19"/>
         <v>-0.23559999999999998</v>
       </c>
-      <c r="V119" s="4"/>
-      <c r="W119" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X119" s="11">
-        <f t="shared" si="16"/>
-        <v>-348.42954159592534</v>
-      </c>
-      <c r="Y119" s="11">
-        <f t="shared" si="20"/>
-        <v>-348.42954159592534</v>
-      </c>
-      <c r="Z119" s="11">
-        <v>-0.3604</v>
-      </c>
-      <c r="AA119" s="11">
-        <v>-0.12479999999999999</v>
-      </c>
-      <c r="AB119" s="11">
-        <v>-0.17460000000000001</v>
-      </c>
-      <c r="AC119" s="11">
-        <v>-0.35780000000000001</v>
-      </c>
-      <c r="AD119" s="11">
-        <v>-0.1832</v>
-      </c>
-      <c r="AE119" s="11">
-        <v>0.36159999999999998</v>
-      </c>
-      <c r="AF119" s="11">
-        <v>4.1176000000000004</v>
-      </c>
-      <c r="AG119" s="11">
-        <v>5.7633999999999999</v>
-      </c>
-      <c r="AH119" s="11">
-        <v>15.0108</v>
-      </c>
-      <c r="AI119" s="11">
-        <v>18.382400000000001</v>
-      </c>
-      <c r="AJ119" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK119" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>167</v>
       </c>
@@ -14306,7 +14766,7 @@
         <v>74</v>
       </c>
       <c r="L120" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
       <c r="M120" s="11"/>
@@ -14320,7 +14780,7 @@
       <c r="S120" s="11"/>
       <c r="T120" s="11"/>
       <c r="U120" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.6</v>
       </c>
       <c r="V120" s="4">
@@ -14328,15 +14788,15 @@
         <v>73.8</v>
       </c>
       <c r="W120" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>73.8</v>
       </c>
       <c r="X120" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8</v>
       </c>
       <c r="Y120" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.1428571428571428</v>
       </c>
       <c r="Z120" s="11">
@@ -14373,11 +14833,15 @@
         <v>164</v>
       </c>
       <c r="AK120" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="121" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL120">
+        <f t="shared" si="19"/>
+        <v>1.1339999999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>168</v>
       </c>
@@ -14398,7 +14862,7 @@
       <c r="J121" s="8"/>
       <c r="K121" s="8"/>
       <c r="L121" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M121" s="8"/>
@@ -14412,20 +14876,20 @@
       <c r="S121" s="8"/>
       <c r="T121" s="8"/>
       <c r="U121" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V121" s="10"/>
       <c r="W121" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X121" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y121" s="11" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z121" s="8">
@@ -14462,11 +14926,15 @@
         <v>45</v>
       </c>
       <c r="AK121" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL121">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>169</v>
       </c>
@@ -14499,7 +14967,7 @@
         <v>338.3</v>
       </c>
       <c r="L122" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>13.142999999999972</v>
       </c>
       <c r="M122" s="11"/>
@@ -14513,7 +14981,7 @@
       <c r="S122" s="11"/>
       <c r="T122" s="11"/>
       <c r="U122" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>70.288600000000002</v>
       </c>
       <c r="V122" s="4">
@@ -14521,15 +14989,15 @@
         <v>39.766150800000332</v>
       </c>
       <c r="W122" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>39.766150800000332</v>
       </c>
       <c r="X122" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y122" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.434244659873716</v>
       </c>
       <c r="Z122" s="11">
@@ -14564,11 +15032,15 @@
       </c>
       <c r="AJ122" s="11"/>
       <c r="AK122" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="123" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL122">
+        <f t="shared" si="19"/>
+        <v>70.288600000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>170</v>
       </c>
@@ -14601,7 +15073,7 @@
         <v>451.55</v>
       </c>
       <c r="L123" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>16.435000000000002</v>
       </c>
       <c r="M123" s="11"/>
@@ -14617,7 +15089,7 @@
       <c r="S123" s="11"/>
       <c r="T123" s="11"/>
       <c r="U123" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>93.597000000000008</v>
       </c>
       <c r="V123" s="4">
@@ -14629,11 +15101,11 @@
         <v>146.17677079999979</v>
       </c>
       <c r="X123" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Y123" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.438232306591024</v>
       </c>
       <c r="Z123" s="11">
@@ -14668,11 +15140,15 @@
       </c>
       <c r="AJ123" s="11"/>
       <c r="AK123" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="124" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL123">
+        <f t="shared" si="19"/>
+        <v>93.597000000000008</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>171</v>
       </c>
@@ -14705,7 +15181,7 @@
         <v>153.4</v>
       </c>
       <c r="L124" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4.3599999999999852</v>
       </c>
       <c r="M124" s="11"/>
@@ -14719,59 +15195,63 @@
       <c r="S124" s="11"/>
       <c r="T124" s="11"/>
       <c r="U124" s="11">
+        <f t="shared" si="21"/>
+        <v>31.552</v>
+      </c>
+      <c r="V124" s="4"/>
+      <c r="W124" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X124" s="11">
+        <f t="shared" si="17"/>
+        <v>14.222736225912779</v>
+      </c>
+      <c r="Y124" s="11">
+        <f t="shared" si="22"/>
+        <v>14.222736225912779</v>
+      </c>
+      <c r="Z124" s="11">
+        <v>45.125</v>
+      </c>
+      <c r="AA124" s="11">
+        <v>47.799799999999998</v>
+      </c>
+      <c r="AB124" s="11">
+        <v>34.2012</v>
+      </c>
+      <c r="AC124" s="11">
+        <v>29.3096</v>
+      </c>
+      <c r="AD124" s="11">
+        <v>30.529399999999999</v>
+      </c>
+      <c r="AE124" s="11">
+        <v>31.781199999999998</v>
+      </c>
+      <c r="AF124" s="11">
+        <v>32.8658</v>
+      </c>
+      <c r="AG124" s="11">
+        <v>29.383600000000001</v>
+      </c>
+      <c r="AH124" s="11">
+        <v>24.572399999999998</v>
+      </c>
+      <c r="AI124" s="11">
+        <v>27.509399999999999</v>
+      </c>
+      <c r="AJ124" s="11"/>
+      <c r="AK124" s="11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL124">
         <f t="shared" si="19"/>
         <v>31.552</v>
       </c>
-      <c r="V124" s="4"/>
-      <c r="W124" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X124" s="11">
-        <f t="shared" si="16"/>
-        <v>14.222736225912779</v>
-      </c>
-      <c r="Y124" s="11">
-        <f t="shared" si="20"/>
-        <v>14.222736225912779</v>
-      </c>
-      <c r="Z124" s="11">
-        <v>45.125</v>
-      </c>
-      <c r="AA124" s="11">
-        <v>47.799799999999998</v>
-      </c>
-      <c r="AB124" s="11">
-        <v>34.2012</v>
-      </c>
-      <c r="AC124" s="11">
-        <v>29.3096</v>
-      </c>
-      <c r="AD124" s="11">
-        <v>30.529399999999999</v>
-      </c>
-      <c r="AE124" s="11">
-        <v>31.781199999999998</v>
-      </c>
-      <c r="AF124" s="11">
-        <v>32.8658</v>
-      </c>
-      <c r="AG124" s="11">
-        <v>29.383600000000001</v>
-      </c>
-      <c r="AH124" s="11">
-        <v>24.572399999999998</v>
-      </c>
-      <c r="AI124" s="11">
-        <v>27.509399999999999</v>
-      </c>
-      <c r="AJ124" s="11"/>
-      <c r="AK124" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>172</v>
       </c>
@@ -14804,7 +15284,7 @@
         <v>1576.05</v>
       </c>
       <c r="L125" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.2570000000000618</v>
       </c>
       <c r="M125" s="11"/>
@@ -14822,59 +15302,63 @@
       <c r="S125" s="11"/>
       <c r="T125" s="11"/>
       <c r="U125" s="11">
+        <f t="shared" si="21"/>
+        <v>316.26139999999998</v>
+      </c>
+      <c r="V125" s="4"/>
+      <c r="W125" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X125" s="11">
+        <f t="shared" si="17"/>
+        <v>11.625171678238321</v>
+      </c>
+      <c r="Y125" s="11">
+        <f t="shared" si="22"/>
+        <v>11.625171678238321</v>
+      </c>
+      <c r="Z125" s="11">
+        <v>312.13819999999998</v>
+      </c>
+      <c r="AA125" s="11">
+        <v>312.54939999999999</v>
+      </c>
+      <c r="AB125" s="11">
+        <v>297.05020000000002</v>
+      </c>
+      <c r="AC125" s="11">
+        <v>289.678</v>
+      </c>
+      <c r="AD125" s="11">
+        <v>290.18599999999998</v>
+      </c>
+      <c r="AE125" s="11">
+        <v>287.87099999999998</v>
+      </c>
+      <c r="AF125" s="11">
+        <v>292.56079999999997</v>
+      </c>
+      <c r="AG125" s="11">
+        <v>311.30119999999999</v>
+      </c>
+      <c r="AH125" s="11">
+        <v>194.2492</v>
+      </c>
+      <c r="AI125" s="11">
+        <v>172.9366</v>
+      </c>
+      <c r="AJ125" s="11"/>
+      <c r="AK125" s="11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL125">
         <f t="shared" si="19"/>
         <v>316.26139999999998</v>
       </c>
-      <c r="V125" s="4"/>
-      <c r="W125" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X125" s="11">
-        <f t="shared" si="16"/>
-        <v>11.625171678238321</v>
-      </c>
-      <c r="Y125" s="11">
-        <f t="shared" si="20"/>
-        <v>11.625171678238321</v>
-      </c>
-      <c r="Z125" s="11">
-        <v>312.13819999999998</v>
-      </c>
-      <c r="AA125" s="11">
-        <v>312.54939999999999</v>
-      </c>
-      <c r="AB125" s="11">
-        <v>297.05020000000002</v>
-      </c>
-      <c r="AC125" s="11">
-        <v>289.678</v>
-      </c>
-      <c r="AD125" s="11">
-        <v>290.18599999999998</v>
-      </c>
-      <c r="AE125" s="11">
-        <v>287.87099999999998</v>
-      </c>
-      <c r="AF125" s="11">
-        <v>292.56079999999997</v>
-      </c>
-      <c r="AG125" s="11">
-        <v>311.30119999999999</v>
-      </c>
-      <c r="AH125" s="11">
-        <v>194.2492</v>
-      </c>
-      <c r="AI125" s="11">
-        <v>172.9366</v>
-      </c>
-      <c r="AJ125" s="11"/>
-      <c r="AK125" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>173</v>
       </c>
@@ -14905,7 +15389,7 @@
         <v>40</v>
       </c>
       <c r="L126" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M126" s="11"/>
@@ -14921,20 +15405,20 @@
       <c r="S126" s="11"/>
       <c r="T126" s="11"/>
       <c r="U126" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="V126" s="4"/>
       <c r="W126" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X126" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>52.75</v>
       </c>
       <c r="Y126" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>52.75</v>
       </c>
       <c r="Z126" s="11">
@@ -14971,11 +15455,15 @@
         <v>174</v>
       </c>
       <c r="AK126" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL126">
+        <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>175</v>
       </c>
@@ -15008,7 +15496,7 @@
         <v>25</v>
       </c>
       <c r="L127" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="M127" s="11"/>
@@ -15024,20 +15512,20 @@
       <c r="S127" s="11"/>
       <c r="T127" s="11"/>
       <c r="U127" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>5.4</v>
       </c>
       <c r="V127" s="4"/>
       <c r="W127" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X127" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>91.1111111111111</v>
       </c>
       <c r="Y127" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>91.1111111111111</v>
       </c>
       <c r="Z127" s="11">
@@ -15074,11 +15562,15 @@
         <v>174</v>
       </c>
       <c r="AK127" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL127">
+        <f t="shared" si="19"/>
+        <v>1.7550000000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>176</v>
       </c>
@@ -15107,7 +15599,7 @@
         <v>39</v>
       </c>
       <c r="L128" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M128" s="11"/>
@@ -15121,20 +15613,20 @@
       <c r="S128" s="11"/>
       <c r="T128" s="11"/>
       <c r="U128" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>7.8</v>
       </c>
       <c r="V128" s="4"/>
       <c r="W128" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X128" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>13.846153846153847</v>
       </c>
       <c r="Y128" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>13.846153846153847</v>
       </c>
       <c r="Z128" s="11">
@@ -15171,11 +15663,15 @@
         <v>177</v>
       </c>
       <c r="AK128" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL128">
+        <f t="shared" si="19"/>
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>178</v>
       </c>
@@ -15206,7 +15702,7 @@
         <v>136</v>
       </c>
       <c r="L129" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-141</v>
       </c>
       <c r="M129" s="11"/>
@@ -15226,22 +15722,22 @@
       </c>
       <c r="T129" s="11"/>
       <c r="U129" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="V129" s="4">
         <v>200</v>
       </c>
       <c r="W129" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>200</v>
       </c>
       <c r="X129" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-201</v>
       </c>
       <c r="Y129" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="Z129" s="11">
@@ -15276,11 +15772,15 @@
       </c>
       <c r="AJ129" s="11"/>
       <c r="AK129" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="130" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL129">
+        <f t="shared" si="19"/>
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>179</v>
       </c>
@@ -15311,7 +15811,7 @@
         <v>15</v>
       </c>
       <c r="L130" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-30</v>
       </c>
       <c r="M130" s="11"/>
@@ -15331,22 +15831,22 @@
       </c>
       <c r="T130" s="11"/>
       <c r="U130" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-3</v>
       </c>
       <c r="V130" s="4">
         <v>150</v>
       </c>
       <c r="W130" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="X130" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-47.111111111111107</v>
       </c>
       <c r="Y130" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.8888888888888906</v>
       </c>
       <c r="Z130" s="11">
@@ -15381,11 +15881,15 @@
       </c>
       <c r="AJ130" s="11"/>
       <c r="AK130" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="131" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL130">
+        <f t="shared" si="19"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>180</v>
       </c>
@@ -15418,7 +15922,7 @@
         <v>292.10000000000002</v>
       </c>
       <c r="L131" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-3.1750000000000114</v>
       </c>
       <c r="M131" s="11"/>
@@ -15434,7 +15938,7 @@
       <c r="S131" s="11"/>
       <c r="T131" s="11"/>
       <c r="U131" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>57.785000000000004</v>
       </c>
       <c r="V131" s="4">
@@ -15442,15 +15946,15 @@
         <v>28.824471000000131</v>
       </c>
       <c r="W131" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28.824471000000131</v>
       </c>
       <c r="X131" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="Y131" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.501177277840267</v>
       </c>
       <c r="Z131" s="11">
@@ -15485,11 +15989,15 @@
       </c>
       <c r="AJ131" s="11"/>
       <c r="AK131" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="132" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL131">
+        <f t="shared" si="19"/>
+        <v>57.785000000000004</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>181</v>
       </c>
@@ -15522,7 +16030,7 @@
         <v>340</v>
       </c>
       <c r="L132" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-117</v>
       </c>
       <c r="M132" s="11"/>
@@ -15540,22 +16048,22 @@
       <c r="S132" s="11"/>
       <c r="T132" s="11"/>
       <c r="U132" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>44.6</v>
       </c>
       <c r="V132" s="4">
         <v>150</v>
       </c>
       <c r="W132" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="X132" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.928251121076233</v>
       </c>
       <c r="Y132" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3.5650224215246635</v>
       </c>
       <c r="Z132" s="11">
@@ -15590,11 +16098,15 @@
       </c>
       <c r="AJ132" s="11"/>
       <c r="AK132" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="133" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL132">
+        <f t="shared" si="19"/>
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>182</v>
       </c>
@@ -15627,7 +16139,7 @@
         <v>108</v>
       </c>
       <c r="L133" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-9</v>
       </c>
       <c r="M133" s="11"/>
@@ -15647,22 +16159,22 @@
       </c>
       <c r="T133" s="11"/>
       <c r="U133" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>19.8</v>
       </c>
       <c r="V133" s="4">
         <v>40</v>
       </c>
       <c r="W133" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>40</v>
       </c>
       <c r="X133" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.5841750841750826</v>
       </c>
       <c r="Y133" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.5639730639730622</v>
       </c>
       <c r="Z133" s="11">
@@ -15697,11 +16209,15 @@
       </c>
       <c r="AJ133" s="11"/>
       <c r="AK133" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL133">
+        <f t="shared" si="19"/>
+        <v>2.3759999999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>183</v>
       </c>
@@ -15732,7 +16248,7 @@
         <v>2</v>
       </c>
       <c r="L134" s="8">
-        <f t="shared" ref="L134" si="21">E134-K134</f>
+        <f t="shared" ref="L134" si="23">E134-K134</f>
         <v>0</v>
       </c>
       <c r="M134" s="8"/>
@@ -15746,20 +16262,20 @@
       <c r="S134" s="8"/>
       <c r="T134" s="8"/>
       <c r="U134" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.4</v>
       </c>
       <c r="V134" s="10"/>
       <c r="W134" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X134" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>120</v>
       </c>
       <c r="Y134" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>120</v>
       </c>
       <c r="Z134" s="8">
@@ -15794,11 +16310,15 @@
       </c>
       <c r="AJ134" s="8"/>
       <c r="AK134" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:37" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A135" s="11"/>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -15837,7 +16357,7 @@
       <c r="AJ135" s="11"/>
       <c r="AK135" s="11"/>
     </row>
-    <row r="136" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A136" s="11"/>
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
@@ -15876,7 +16396,7 @@
       <c r="AJ136" s="11"/>
       <c r="AK136" s="11"/>
     </row>
-    <row r="137" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A137" s="11"/>
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
@@ -15915,7 +16435,7 @@
       <c r="AJ137" s="11"/>
       <c r="AK137" s="11"/>
     </row>
-    <row r="138" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A138" s="11"/>
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
@@ -15954,7 +16474,7 @@
       <c r="AJ138" s="11"/>
       <c r="AK138" s="11"/>
     </row>
-    <row r="139" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A139" s="11"/>
       <c r="B139" s="11"/>
       <c r="C139" s="11"/>
@@ -15993,7 +16513,7 @@
       <c r="AJ139" s="11"/>
       <c r="AK139" s="11"/>
     </row>
-    <row r="140" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A140" s="11"/>
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
@@ -16032,7 +16552,7 @@
       <c r="AJ140" s="11"/>
       <c r="AK140" s="11"/>
     </row>
-    <row r="141" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A141" s="11"/>
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
@@ -16071,7 +16591,7 @@
       <c r="AJ141" s="11"/>
       <c r="AK141" s="11"/>
     </row>
-    <row r="142" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A142" s="11"/>
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
@@ -16110,7 +16630,7 @@
       <c r="AJ142" s="11"/>
       <c r="AK142" s="11"/>
     </row>
-    <row r="143" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A143" s="11"/>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -16149,7 +16669,7 @@
       <c r="AJ143" s="11"/>
       <c r="AK143" s="11"/>
     </row>
-    <row r="144" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A144" s="11"/>
       <c r="B144" s="11"/>
       <c r="C144" s="11"/>
